--- a/Data/FlightPlan/FPL_19SEP26.xlsx
+++ b/Data/FlightPlan/FPL_19SEP26.xlsx
@@ -254,6 +254,117 @@
     <t>19:50</t>
   </si>
   <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A522</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A523</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
     <t>NGO</t>
   </si>
   <si>
@@ -263,108 +374,6 @@
     <t>08:00</t>
   </si>
   <si>
-    <t>VN-A522</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>DAD</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A523</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
     <t>VN-A529</t>
   </si>
   <si>
@@ -449,15 +458,6 @@
     <t>17:40</t>
   </si>
   <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
     <t>VN-A536</t>
   </si>
   <si>
@@ -497,48 +497,48 @@
     <t>HPH</t>
   </si>
   <si>
+    <t>18:15</t>
+  </si>
+  <si>
     <t>20:15</t>
   </si>
   <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
     <t>22:15</t>
   </si>
   <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
     <t>23:55</t>
   </si>
   <si>
@@ -1229,7 +1229,7 @@
     <t>Total Record(s): 398</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 18, 2026 22:37</t>
+    <t xml:space="preserve">Generated on  Sep 19, 2026 00:12</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2647,10 +2647,10 @@
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c t="s" r="A36" s="6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B36" s="7">
-        <v>920</v>
+        <v>7526</v>
       </c>
       <c t="s" r="C36" s="7">
         <v>14</v>
@@ -2666,62 +2666,62 @@
         <v>37</v>
       </c>
       <c t="s" r="H36" s="8">
+        <v>28</v>
+      </c>
+      <c t="s" r="I36" s="7">
         <v>81</v>
       </c>
-      <c t="s" r="I36" s="7">
-        <v>82</v>
-      </c>
       <c t="s" r="J36" s="7">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
       <c r="M36" s="7"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
+      <c t="s" r="A37" s="6">
+        <v>31</v>
+      </c>
+      <c r="B37" s="7">
+        <v>7527</v>
+      </c>
+      <c t="s" r="C37" s="7">
+        <v>14</v>
+      </c>
       <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
+      <c t="s" r="E37" s="7">
+        <v>73</v>
+      </c>
+      <c r="F37" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G37" s="8">
+        <v>28</v>
+      </c>
+      <c t="s" r="H37" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="I37" s="7">
+        <v>82</v>
+      </c>
+      <c t="s" r="J37" s="7">
+        <v>83</v>
+      </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
       <c r="M37" s="7"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c t="s" r="A38" s="6">
-        <v>13</v>
-      </c>
-      <c r="B38" s="7">
-        <v>260</v>
-      </c>
-      <c t="s" r="C38" s="7">
-        <v>14</v>
-      </c>
+      <c r="A38" s="6"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c t="s" r="E38" s="7">
-        <v>84</v>
-      </c>
-      <c r="F38" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G38" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H38" s="8">
-        <v>85</v>
-      </c>
-      <c t="s" r="I38" s="7">
-        <v>86</v>
-      </c>
-      <c t="s" r="J38" s="7">
-        <v>87</v>
-      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
@@ -2731,7 +2731,7 @@
         <v>13</v>
       </c>
       <c r="B39" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="C39" s="7">
         <v>14</v>
@@ -2744,16 +2744,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G39" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H39" s="8">
         <v>85</v>
       </c>
-      <c t="s" r="H39" s="8">
-        <v>25</v>
-      </c>
       <c t="s" r="I39" s="7">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2764,7 +2764,7 @@
         <v>13</v>
       </c>
       <c r="B40" s="7">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c t="s" r="C40" s="7">
         <v>14</v>
@@ -2777,16 +2777,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G40" s="8">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2797,7 +2797,7 @@
         <v>13</v>
       </c>
       <c r="B41" s="7">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="C41" s="7">
         <v>14</v>
@@ -2810,16 +2810,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H41" s="8">
         <v>90</v>
       </c>
-      <c t="s" r="H41" s="8">
-        <v>25</v>
-      </c>
       <c t="s" r="I41" s="7">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2830,7 +2830,7 @@
         <v>13</v>
       </c>
       <c r="B42" s="7">
-        <v>144</v>
+        <v>245</v>
       </c>
       <c t="s" r="C42" s="7">
         <v>14</v>
@@ -2843,16 +2843,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c t="s" r="H42" s="8">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2863,7 +2863,7 @@
         <v>13</v>
       </c>
       <c r="B43" s="7">
-        <v>519</v>
+        <v>144</v>
       </c>
       <c t="s" r="C43" s="7">
         <v>14</v>
@@ -2876,16 +2876,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G43" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H43" s="8">
         <v>37</v>
       </c>
-      <c t="s" r="H43" s="8">
-        <v>96</v>
-      </c>
       <c t="s" r="I43" s="7">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2896,7 +2896,7 @@
         <v>13</v>
       </c>
       <c r="B44" s="7">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c t="s" r="C44" s="7">
         <v>14</v>
@@ -2909,16 +2909,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="H44" s="8">
         <v>96</v>
       </c>
-      <c t="s" r="H44" s="8">
-        <v>37</v>
-      </c>
       <c t="s" r="I44" s="7">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2929,7 +2929,7 @@
         <v>13</v>
       </c>
       <c r="B45" s="7">
-        <v>169</v>
+        <v>522</v>
       </c>
       <c t="s" r="C45" s="7">
         <v>14</v>
@@ -2942,65 +2942,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G45" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H45" s="8">
         <v>37</v>
       </c>
-      <c t="s" r="H45" s="8">
-        <v>25</v>
-      </c>
       <c t="s" r="I45" s="7">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="6"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
+      <c t="s" r="A46" s="6">
+        <v>13</v>
+      </c>
+      <c r="B46" s="7">
+        <v>169</v>
+      </c>
+      <c t="s" r="C46" s="7">
+        <v>14</v>
+      </c>
       <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
+      <c t="s" r="E46" s="7">
+        <v>84</v>
+      </c>
+      <c r="F46" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G46" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="H46" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I46" s="7">
+        <v>101</v>
+      </c>
+      <c t="s" r="J46" s="7">
+        <v>102</v>
+      </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c t="s" r="A47" s="6">
-        <v>13</v>
-      </c>
-      <c r="B47" s="7">
-        <v>852</v>
-      </c>
-      <c t="s" r="C47" s="7">
-        <v>14</v>
-      </c>
+      <c r="A47" s="6"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
       <c r="D47" s="7"/>
-      <c t="s" r="E47" s="7">
-        <v>103</v>
-      </c>
-      <c r="F47" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G47" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H47" s="8">
-        <v>76</v>
-      </c>
-      <c t="s" r="I47" s="7">
-        <v>104</v>
-      </c>
-      <c t="s" r="J47" s="7">
-        <v>57</v>
-      </c>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
@@ -3010,7 +3010,7 @@
         <v>13</v>
       </c>
       <c r="B48" s="7">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c t="s" r="C48" s="7">
         <v>14</v>
@@ -3023,65 +3023,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H48" s="8">
         <v>76</v>
       </c>
-      <c t="s" r="H48" s="8">
-        <v>25</v>
-      </c>
       <c t="s" r="I48" s="7">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c r="M48" s="7"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="6"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
+      <c t="s" r="A49" s="6">
+        <v>13</v>
+      </c>
+      <c r="B49" s="7">
+        <v>853</v>
+      </c>
+      <c t="s" r="C49" s="7">
+        <v>14</v>
+      </c>
       <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
+      <c t="s" r="E49" s="7">
+        <v>103</v>
+      </c>
+      <c r="F49" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G49" s="8">
+        <v>76</v>
+      </c>
+      <c t="s" r="H49" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I49" s="7">
+        <v>58</v>
+      </c>
+      <c t="s" r="J49" s="7">
+        <v>79</v>
+      </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
       <c r="M49" s="7"/>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c t="s" r="A50" s="6">
-        <v>13</v>
-      </c>
-      <c r="B50" s="7">
-        <v>8512</v>
-      </c>
-      <c t="s" r="C50" s="7">
-        <v>14</v>
-      </c>
+      <c r="A50" s="6"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
       <c r="D50" s="7"/>
-      <c t="s" r="E50" s="7">
-        <v>105</v>
-      </c>
-      <c r="F50" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G50" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="H50" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="I50" s="7">
-        <v>106</v>
-      </c>
-      <c t="s" r="J50" s="7">
-        <v>107</v>
-      </c>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
       <c r="M50" s="7"/>
@@ -3091,7 +3091,7 @@
         <v>13</v>
       </c>
       <c r="B51" s="7">
-        <v>8513</v>
+        <v>8512</v>
       </c>
       <c t="s" r="C51" s="7">
         <v>14</v>
@@ -3104,16 +3104,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H51" s="8">
         <v>67</v>
       </c>
-      <c t="s" r="H51" s="8">
-        <v>96</v>
-      </c>
       <c t="s" r="I51" s="7">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3124,7 +3124,7 @@
         <v>13</v>
       </c>
       <c r="B52" s="7">
-        <v>878</v>
+        <v>8513</v>
       </c>
       <c t="s" r="C52" s="7">
         <v>14</v>
@@ -3137,65 +3137,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G52" s="8">
+        <v>67</v>
+      </c>
+      <c t="s" r="H52" s="8">
         <v>96</v>
       </c>
-      <c t="s" r="H52" s="8">
-        <v>64</v>
-      </c>
       <c t="s" r="I52" s="7">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
-      <c r="A53" s="6"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
+      <c t="s" r="A53" s="6">
+        <v>13</v>
+      </c>
+      <c r="B53" s="7">
+        <v>878</v>
+      </c>
+      <c t="s" r="C53" s="7">
+        <v>14</v>
+      </c>
       <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
+      <c t="s" r="E53" s="7">
+        <v>105</v>
+      </c>
+      <c r="F53" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G53" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H53" s="8">
+        <v>64</v>
+      </c>
+      <c t="s" r="I53" s="7">
+        <v>110</v>
+      </c>
+      <c t="s" r="J53" s="7">
+        <v>111</v>
+      </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c t="s" r="A54" s="6">
-        <v>13</v>
-      </c>
-      <c r="B54" s="7">
-        <v>7707</v>
-      </c>
-      <c t="s" r="C54" s="7">
-        <v>34</v>
-      </c>
+      <c r="A54" s="6"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
       <c r="D54" s="7"/>
-      <c t="s" r="E54" s="7">
-        <v>112</v>
-      </c>
-      <c r="F54" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G54" s="8">
-        <v>113</v>
-      </c>
-      <c t="s" r="H54" s="8">
-        <v>37</v>
-      </c>
-      <c t="s" r="I54" s="7">
-        <v>114</v>
-      </c>
-      <c t="s" r="J54" s="7">
-        <v>39</v>
-      </c>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
@@ -3218,16 +3218,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
+        <v>113</v>
+      </c>
+      <c t="s" r="H55" s="8">
         <v>37</v>
       </c>
-      <c t="s" r="H55" s="8">
-        <v>115</v>
-      </c>
       <c t="s" r="I55" s="7">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3238,10 +3238,10 @@
         <v>13</v>
       </c>
       <c r="B56" s="7">
-        <v>776</v>
+        <v>7707</v>
       </c>
       <c t="s" r="C56" s="7">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
@@ -3251,156 +3251,152 @@
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="H56" s="8">
         <v>115</v>
       </c>
-      <c t="s" r="H56" s="8">
-        <v>37</v>
-      </c>
       <c t="s" r="I56" s="7">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c r="M56" s="7"/>
     </row>
     <row r="57" ht="14.25" customHeight="1">
-      <c r="A57" s="6"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
+      <c t="s" r="A57" s="6">
+        <v>13</v>
+      </c>
+      <c r="B57" s="7">
+        <v>776</v>
+      </c>
+      <c t="s" r="C57" s="7">
+        <v>14</v>
+      </c>
       <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
+      <c t="s" r="E57" s="7">
+        <v>112</v>
+      </c>
+      <c r="F57" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G57" s="8">
+        <v>115</v>
+      </c>
+      <c t="s" r="H57" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="I57" s="7">
+        <v>117</v>
+      </c>
+      <c t="s" r="J57" s="7">
+        <v>27</v>
+      </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c r="M57" s="7"/>
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c t="s" r="A58" s="6">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B58" s="7">
-        <v>869</v>
+        <v>920</v>
       </c>
       <c t="s" r="C58" s="7">
         <v>14</v>
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
+        <v>112</v>
+      </c>
+      <c r="F58" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G58" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="H58" s="8">
         <v>118</v>
       </c>
-      <c r="F58" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G58" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H58" s="8">
-        <v>25</v>
-      </c>
       <c t="s" r="I58" s="7">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>119</v>
-      </c>
-      <c t="s" r="K58" s="7">
         <v>120</v>
       </c>
+      <c r="K58" s="7"/>
       <c r="L58" s="7"/>
-      <c t="s" r="M58" s="7">
-        <v>121</v>
-      </c>
+      <c r="M58" s="7"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c t="s" r="A59" s="6">
-        <v>13</v>
-      </c>
-      <c r="B59" s="7">
-        <v>860</v>
-      </c>
-      <c t="s" r="C59" s="7">
-        <v>14</v>
-      </c>
+      <c r="A59" s="6"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
       <c r="D59" s="7"/>
-      <c t="s" r="E59" s="7">
-        <v>118</v>
-      </c>
-      <c r="F59" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G59" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H59" s="8">
-        <v>64</v>
-      </c>
-      <c t="s" r="I59" s="7">
-        <v>75</v>
-      </c>
-      <c t="s" r="J59" s="7">
-        <v>26</v>
-      </c>
-      <c t="s" r="K59" s="7">
-        <v>122</v>
-      </c>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
       <c r="L59" s="7"/>
-      <c t="s" r="M59" s="7">
-        <v>80</v>
-      </c>
+      <c r="M59" s="7"/>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c t="s" r="A60" s="6">
         <v>13</v>
       </c>
       <c r="B60" s="7">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c t="s" r="C60" s="7">
         <v>14</v>
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I60" s="7">
+        <v>87</v>
+      </c>
+      <c t="s" r="J60" s="7">
+        <v>122</v>
+      </c>
+      <c t="s" r="K60" s="7">
         <v>123</v>
       </c>
-      <c t="s" r="J60" s="7">
+      <c r="L60" s="7"/>
+      <c t="s" r="M60" s="7">
         <v>124</v>
       </c>
-      <c r="K60" s="7"/>
-      <c r="L60" s="7"/>
-      <c r="M60" s="7"/>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c t="s" r="A61" s="6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B61" s="7">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c t="s" r="C61" s="7">
         <v>14</v>
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3412,92 +3408,96 @@
         <v>64</v>
       </c>
       <c t="s" r="I61" s="7">
+        <v>75</v>
+      </c>
+      <c t="s" r="J61" s="7">
+        <v>26</v>
+      </c>
+      <c t="s" r="K61" s="7">
         <v>125</v>
       </c>
-      <c t="s" r="J61" s="7">
+      <c r="L61" s="7"/>
+      <c t="s" r="M61" s="7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25" customHeight="1">
+      <c t="s" r="A62" s="6">
+        <v>13</v>
+      </c>
+      <c r="B62" s="7">
+        <v>861</v>
+      </c>
+      <c t="s" r="C62" s="7">
+        <v>14</v>
+      </c>
+      <c r="D62" s="7"/>
+      <c t="s" r="E62" s="7">
+        <v>121</v>
+      </c>
+      <c r="F62" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G62" s="8">
+        <v>64</v>
+      </c>
+      <c t="s" r="H62" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I62" s="7">
         <v>126</v>
       </c>
-      <c r="K61" s="7"/>
-      <c r="L61" s="7"/>
-      <c r="M61" s="7"/>
-    </row>
-    <row r="62" ht="14.25" customHeight="1">
-      <c r="A62" s="6"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
+      <c t="s" r="J62" s="7">
+        <v>127</v>
+      </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c r="M62" s="7"/>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c t="s" r="A63" s="6">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B63" s="7">
-        <v>129</v>
+        <v>862</v>
       </c>
       <c t="s" r="C63" s="7">
         <v>14</v>
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c t="s" r="I63" s="7">
         <v>128</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c t="s" r="A64" s="6">
-        <v>13</v>
-      </c>
-      <c r="B64" s="7">
-        <v>335</v>
-      </c>
-      <c t="s" r="C64" s="7">
-        <v>14</v>
-      </c>
+      <c r="A64" s="6"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
       <c r="D64" s="7"/>
-      <c t="s" r="E64" s="7">
-        <v>127</v>
-      </c>
-      <c r="F64" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G64" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H64" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I64" s="7">
-        <v>129</v>
-      </c>
-      <c t="s" r="J64" s="7">
-        <v>106</v>
-      </c>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
@@ -3507,29 +3507,29 @@
         <v>13</v>
       </c>
       <c r="B65" s="7">
-        <v>338</v>
+        <v>129</v>
       </c>
       <c t="s" r="C65" s="7">
         <v>14</v>
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3540,14 +3540,14 @@
         <v>13</v>
       </c>
       <c r="B66" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c t="s" r="C66" s="7">
         <v>14</v>
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3559,10 +3559,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3573,14 +3573,14 @@
         <v>13</v>
       </c>
       <c r="B67" s="7">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c t="s" r="C67" s="7">
         <v>14</v>
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3595,7 +3595,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3606,14 +3606,14 @@
         <v>13</v>
       </c>
       <c r="B68" s="7">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c t="s" r="C68" s="7">
         <v>14</v>
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H68" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I68" s="7">
+        <v>134</v>
+      </c>
+      <c t="s" r="J68" s="7">
         <v>135</v>
-      </c>
-      <c t="s" r="I68" s="7">
-        <v>136</v>
-      </c>
-      <c t="s" r="J68" s="7">
-        <v>97</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3639,45 +3639,63 @@
         <v>13</v>
       </c>
       <c r="B69" s="7">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c t="s" r="C69" s="7">
         <v>14</v>
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>135</v>
+        <v>17</v>
       </c>
       <c t="s" r="H69" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I69" s="7">
+        <v>136</v>
+      </c>
+      <c t="s" r="J69" s="7">
         <v>137</v>
-      </c>
-      <c t="s" r="J69" s="7">
-        <v>138</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c r="M69" s="7"/>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="6"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
+      <c t="s" r="A70" s="6">
+        <v>13</v>
+      </c>
+      <c r="B70" s="7">
+        <v>312</v>
+      </c>
+      <c t="s" r="C70" s="7">
+        <v>14</v>
+      </c>
       <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
+      <c t="s" r="E70" s="7">
+        <v>130</v>
+      </c>
+      <c r="F70" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G70" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H70" s="8">
+        <v>138</v>
+      </c>
+      <c t="s" r="I70" s="7">
+        <v>139</v>
+      </c>
+      <c t="s" r="J70" s="7">
+        <v>97</v>
+      </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c r="M70" s="7"/>
@@ -3687,63 +3705,45 @@
         <v>13</v>
       </c>
       <c r="B71" s="7">
-        <v>1948</v>
+        <v>311</v>
       </c>
       <c t="s" r="C71" s="7">
         <v>14</v>
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c t="s" r="H71" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I71" s="7">
         <v>140</v>
       </c>
-      <c t="s" r="I71" s="7">
+      <c t="s" r="J71" s="7">
         <v>141</v>
-      </c>
-      <c t="s" r="J71" s="7">
-        <v>89</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c r="M71" s="7"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
-      <c t="s" r="A72" s="6">
-        <v>13</v>
-      </c>
-      <c r="B72" s="7">
-        <v>1949</v>
-      </c>
-      <c t="s" r="C72" s="7">
-        <v>14</v>
-      </c>
+      <c r="A72" s="6"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
       <c r="D72" s="7"/>
-      <c t="s" r="E72" s="7">
-        <v>139</v>
-      </c>
-      <c r="F72" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G72" s="8">
-        <v>140</v>
-      </c>
-      <c t="s" r="H72" s="8">
-        <v>37</v>
-      </c>
-      <c t="s" r="I72" s="7">
-        <v>142</v>
-      </c>
-      <c t="s" r="J72" s="7">
-        <v>143</v>
-      </c>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="7"/>
+      <c r="J72" s="7"/>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c r="M72" s="7"/>
@@ -3753,14 +3753,14 @@
         <v>13</v>
       </c>
       <c r="B73" s="7">
-        <v>145</v>
+        <v>1948</v>
       </c>
       <c t="s" r="C73" s="7">
         <v>14</v>
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3769,13 +3769,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c t="s" r="I73" s="7">
         <v>144</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3786,20 +3786,20 @@
         <v>13</v>
       </c>
       <c r="B74" s="7">
-        <v>150</v>
+        <v>1949</v>
       </c>
       <c t="s" r="C74" s="7">
         <v>14</v>
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>37</v>
@@ -3808,7 +3808,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3819,14 +3819,14 @@
         <v>13</v>
       </c>
       <c r="B75" s="7">
-        <v>7526</v>
+        <v>145</v>
       </c>
       <c t="s" r="C75" s="7">
         <v>14</v>
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -3835,13 +3835,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H75" s="8">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3849,32 +3849,32 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c t="s" r="A76" s="6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B76" s="7">
-        <v>7527</v>
+        <v>150</v>
       </c>
       <c t="s" r="C76" s="7">
         <v>14</v>
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c t="s" r="H76" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3985,7 +3985,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>61</v>
@@ -4129,10 +4129,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c t="s" r="J85" s="7">
         <v>106</v>
@@ -4159,13 +4159,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H86" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>39</v>
@@ -4234,7 +4234,7 @@
         <v>160</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4245,7 +4245,7 @@
         <v>13</v>
       </c>
       <c r="B89" s="7">
-        <v>1282</v>
+        <v>282</v>
       </c>
       <c t="s" r="C89" s="7">
         <v>14</v>
@@ -4444,7 +4444,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>57</v>
@@ -4480,7 +4480,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4591,7 +4591,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>150</v>
@@ -4638,7 +4638,7 @@
         <v>13</v>
       </c>
       <c r="B102" s="7">
-        <v>282</v>
+        <v>1282</v>
       </c>
       <c t="s" r="C102" s="7">
         <v>14</v>
@@ -4657,10 +4657,10 @@
         <v>161</v>
       </c>
       <c t="s" r="I102" s="7">
+        <v>163</v>
+      </c>
+      <c t="s" r="J102" s="7">
         <v>175</v>
-      </c>
-      <c t="s" r="J102" s="7">
-        <v>162</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4771,7 +4771,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J106" s="7">
         <v>181</v>
@@ -4807,7 +4807,7 @@
         <v>182</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4951,7 +4951,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>38</v>
@@ -5380,7 +5380,7 @@
         <v>206</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5410,7 +5410,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>207</v>
@@ -5443,10 +5443,10 @@
         <v>208</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5491,7 +5491,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>210</v>
@@ -5560,7 +5560,7 @@
         <v>213</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5788,7 +5788,7 @@
         <v>222</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5818,7 +5818,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>223</v>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -5898,7 +5898,7 @@
         <v>171</v>
       </c>
       <c t="s" r="K143" s="7">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
@@ -5975,7 +5975,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>37</v>
@@ -6131,7 +6131,7 @@
         <v>222</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6158,7 +6158,7 @@
         <v>37</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I152" s="7">
         <v>173</v>
@@ -6188,7 +6188,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>37</v>
@@ -6239,7 +6239,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I155" s="7">
         <v>186</v>
@@ -6269,7 +6269,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>25</v>
@@ -6278,7 +6278,7 @@
         <v>189</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6392,7 +6392,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6425,7 +6425,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6701,7 +6701,7 @@
         <v>254</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>165</v>
@@ -6881,7 +6881,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>223</v>
@@ -7031,7 +7031,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7061,7 +7061,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>150</v>
@@ -7160,7 +7160,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>265</v>
@@ -7196,7 +7196,7 @@
         <v>267</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7277,7 +7277,7 @@
         <v>180</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7340,7 +7340,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>182</v>
@@ -7406,7 +7406,7 @@
         <v>167</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>274</v>
@@ -7520,7 +7520,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>278</v>
@@ -7556,7 +7556,7 @@
         <v>279</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7655,7 +7655,7 @@
         <v>252</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7766,7 +7766,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>197</v>
@@ -7934,7 +7934,7 @@
         <v>284</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8045,7 +8045,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>260</v>
@@ -8081,7 +8081,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8573,7 +8573,7 @@
         <v>217</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8687,7 +8687,7 @@
         <v>186</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8819,7 +8819,7 @@
         <v>218</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8852,7 +8852,7 @@
         <v>227</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8966,7 +8966,7 @@
         <v>277</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9065,7 +9065,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9110,7 +9110,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>150</v>
@@ -9146,7 +9146,7 @@
         <v>225</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9209,7 +9209,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>46</v>
@@ -9407,7 +9407,7 @@
         <v>168</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9437,7 +9437,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>160</v>
@@ -9470,7 +9470,7 @@
         <v>264</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>98</v>
@@ -9536,7 +9536,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>291</v>
@@ -9587,7 +9587,7 @@
         <v>186</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9716,7 +9716,7 @@
         <v>85</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>274</v>
@@ -10046,7 +10046,7 @@
         <v>319</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10112,7 +10112,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10505,7 +10505,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10601,7 +10601,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>194</v>
@@ -10715,7 +10715,7 @@
         <v>261</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>38</v>
@@ -10880,7 +10880,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>207</v>
@@ -11111,7 +11111,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11325,7 +11325,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>339</v>
@@ -11443,7 +11443,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>342</v>
@@ -11917,10 +11917,10 @@
         <v>211</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11983,7 +11983,7 @@
         <v>345</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>42</v>
@@ -12064,10 +12064,10 @@
         <v>96</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12094,7 +12094,7 @@
         <v>96</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="I348" s="7">
         <v>287</v>
@@ -12124,7 +12124,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>96</v>
@@ -12133,7 +12133,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12244,7 +12244,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>199</v>
@@ -12313,7 +12313,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12385,7 +12385,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>115</v>
@@ -12396,9 +12396,13 @@
       <c t="s" r="J358" s="7">
         <v>181</v>
       </c>
-      <c r="K358" s="7"/>
+      <c t="s" r="K358" s="7">
+        <v>158</v>
+      </c>
       <c r="L358" s="7"/>
-      <c r="M358" s="7"/>
+      <c t="s" r="M358" s="7">
+        <v>320</v>
+      </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
       <c t="s" r="A359" s="6">
@@ -12429,9 +12433,13 @@
       <c t="s" r="J359" s="7">
         <v>159</v>
       </c>
-      <c r="K359" s="7"/>
+      <c t="s" r="K359" s="7">
+        <v>147</v>
+      </c>
       <c r="L359" s="7"/>
-      <c r="M359" s="7"/>
+      <c t="s" r="M359" s="7">
+        <v>22</v>
+      </c>
     </row>
     <row r="360" ht="15" customHeight="1">
       <c t="s" r="A360" s="6">
@@ -12457,7 +12465,7 @@
         <v>359</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>246</v>
@@ -12541,7 +12549,7 @@
         <v>272</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12673,7 +12681,7 @@
         <v>203</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12721,7 +12729,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12754,7 +12762,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12787,7 +12795,7 @@
         <v>213</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12832,10 +12840,10 @@
         <v>169</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12898,10 +12906,10 @@
         <v>169</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13000,7 +13008,7 @@
         <v>201</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13177,7 +13185,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>369</v>
@@ -13207,7 +13215,7 @@
         <v>37</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I385" s="7">
         <v>190</v>
@@ -13237,13 +13245,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>40</v>
@@ -13276,7 +13284,7 @@
         <v>254</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>241</v>
@@ -13393,7 +13401,7 @@
         <v>365</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13636,7 +13644,7 @@
         <v>161</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>331</v>
@@ -13816,10 +13824,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13846,7 +13854,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I406" s="7">
         <v>330</v>
@@ -13876,7 +13884,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>25</v>
@@ -13915,10 +13923,10 @@
         <v>90</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14029,7 +14037,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>218</v>
@@ -14098,7 +14106,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14206,7 +14214,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I418" s="7">
         <v>185</v>
@@ -14236,7 +14244,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>25</v>
@@ -14245,7 +14253,7 @@
         <v>379</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14382,7 +14390,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>201</v>
@@ -14412,13 +14420,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -14442,7 +14450,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H425" s="8">
         <v>25</v>
@@ -14496,7 +14504,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>157</v>
@@ -14532,7 +14540,7 @@
         <v>282</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14697,7 +14705,7 @@
         <v>284</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>146</v>
+        <v>81</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14844,7 +14852,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -14991,7 +14999,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -15024,7 +15032,7 @@
         <v>186</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15051,7 +15059,7 @@
         <v>37</v>
       </c>
       <c t="s" r="H445" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="I445" s="7">
         <v>230</v>
@@ -15081,7 +15089,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G446" s="8">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="H446" s="8">
         <v>37</v>
@@ -15186,7 +15194,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J449" s="7">
         <v>202</v>
@@ -15333,7 +15341,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>294</v>
@@ -15447,7 +15455,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J458" s="7">
         <v>387</v>
@@ -15582,7 +15590,7 @@
         <v>217</v>
       </c>
       <c t="s" r="K463" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
@@ -15613,7 +15621,7 @@
         <v>391</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J464" s="7">
         <v>41</v>
@@ -15653,7 +15661,7 @@
         <v>193</v>
       </c>
       <c t="s" r="J465" s="7">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>

--- a/Data/FlightPlan/FPL_19SEP26.xlsx
+++ b/Data/FlightPlan/FPL_19SEP26.xlsx
@@ -746,258 +746,258 @@
     <t>VN-A629</t>
   </si>
   <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
     <t>VCA</t>
   </si>
   <si>
     <t>21:50</t>
   </si>
   <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:55</t>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
   </si>
   <si>
     <t>UIH</t>
   </si>
   <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
     <t>11:35</t>
   </si>
   <si>
@@ -1046,87 +1046,87 @@
     <t>VN-A668</t>
   </si>
   <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
     <t>PKX</t>
   </si>
   <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
     <t>03:55</t>
   </si>
   <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
     <t>VN-A677</t>
   </si>
   <si>
@@ -1229,7 +1229,7 @@
     <t>Total Record(s): 398</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 19, 2026 00:12</t>
+    <t xml:space="preserve">Generated on  Sep 19, 2026 00:43</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6370,7 +6370,7 @@
         <v>13</v>
       </c>
       <c r="B160" s="7">
-        <v>901</v>
+        <v>403</v>
       </c>
       <c t="s" r="C160" s="7">
         <v>14</v>
@@ -6386,13 +6386,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6403,7 +6403,7 @@
         <v>13</v>
       </c>
       <c r="B161" s="7">
-        <v>902</v>
+        <v>404</v>
       </c>
       <c t="s" r="C161" s="7">
         <v>14</v>
@@ -6416,16 +6416,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6436,7 +6436,7 @@
         <v>13</v>
       </c>
       <c r="B162" s="7">
-        <v>465</v>
+        <v>567</v>
       </c>
       <c t="s" r="C162" s="7">
         <v>14</v>
@@ -6452,13 +6452,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6469,7 +6469,7 @@
         <v>13</v>
       </c>
       <c r="B163" s="7">
-        <v>466</v>
+        <v>568</v>
       </c>
       <c t="s" r="C163" s="7">
         <v>14</v>
@@ -6482,16 +6482,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>51</v>
+        <v>148</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>246</v>
+        <v>40</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6521,10 +6521,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6569,10 +6569,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6668,10 +6668,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6698,7 +6698,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c t="s" r="I170" s="7">
         <v>140</v>
@@ -6722,22 +6722,22 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
+        <v>252</v>
+      </c>
+      <c t="s" r="H171" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I171" s="7">
+        <v>253</v>
+      </c>
+      <c t="s" r="J171" s="7">
         <v>254</v>
-      </c>
-      <c t="s" r="H171" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I171" s="7">
-        <v>255</v>
-      </c>
-      <c t="s" r="J171" s="7">
-        <v>256</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6782,7 +6782,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>66</v>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6815,10 +6815,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6829,14 +6829,14 @@
         <v>13</v>
       </c>
       <c r="B175" s="7">
-        <v>403</v>
+        <v>901</v>
       </c>
       <c t="s" r="C175" s="7">
         <v>14</v>
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6845,13 +6845,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6862,29 +6862,29 @@
         <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>404</v>
+        <v>902</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>223</v>
+        <v>135</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6895,14 +6895,14 @@
         <v>13</v>
       </c>
       <c r="B177" s="7">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c t="s" r="C177" s="7">
         <v>14</v>
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6911,13 +6911,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6928,29 +6928,29 @@
         <v>13</v>
       </c>
       <c r="B178" s="7">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c t="s" r="C178" s="7">
         <v>14</v>
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>26</v>
+        <v>260</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6995,7 +6995,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>68</v>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7091,7 +7091,7 @@
         <v>115</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>223</v>
@@ -7115,13 +7115,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>115</v>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7163,7 +7163,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7190,10 +7190,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H186" s="8">
+        <v>265</v>
+      </c>
+      <c t="s" r="I186" s="7">
         <v>266</v>
-      </c>
-      <c t="s" r="I186" s="7">
-        <v>267</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>82</v>
@@ -7214,22 +7214,22 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I187" s="7">
+        <v>267</v>
+      </c>
+      <c t="s" r="J187" s="7">
         <v>268</v>
-      </c>
-      <c t="s" r="J187" s="7">
-        <v>269</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7271,7 +7271,7 @@
         <v>37</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>180</v>
@@ -7295,19 +7295,19 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
+        <v>269</v>
+      </c>
+      <c r="F190" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G190" s="8">
         <v>270</v>
-      </c>
-      <c r="F190" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G190" s="8">
-        <v>271</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>199</v>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7376,7 +7376,7 @@
         <v>173</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7409,7 +7409,7 @@
         <v>137</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7442,7 +7442,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7487,7 +7487,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>87</v>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7523,7 +7523,7 @@
         <v>131</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7553,7 +7553,7 @@
         <v>169</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>124</v>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7607,7 +7607,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7652,7 +7652,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>162</v>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7685,7 +7685,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>52</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7733,7 +7733,7 @@
         <v>167</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>186</v>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7787,19 +7787,19 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
+        <v>279</v>
+      </c>
+      <c r="F206" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G206" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H206" s="8">
         <v>280</v>
       </c>
-      <c r="F206" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G206" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H206" s="8">
+      <c t="s" r="I206" s="7">
         <v>281</v>
-      </c>
-      <c t="s" r="I206" s="7">
-        <v>282</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>189</v>
@@ -7820,13 +7820,13 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
+        <v>279</v>
+      </c>
+      <c r="F207" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G207" s="8">
         <v>280</v>
-      </c>
-      <c r="F207" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G207" s="8">
-        <v>281</v>
       </c>
       <c t="s" r="H207" s="8">
         <v>25</v>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7865,7 +7865,7 @@
         <v>167</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>40</v>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7931,7 +7931,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>81</v>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7967,7 +7967,7 @@
         <v>164</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8033,7 +8033,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8048,7 +8048,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8111,7 +8111,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>70</v>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8141,7 +8141,7 @@
         <v>37</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="I217" s="7">
         <v>218</v>
@@ -8165,13 +8165,13 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>37</v>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8213,7 +8213,7 @@
         <v>201</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8243,10 +8243,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I220" s="7">
+        <v>287</v>
+      </c>
+      <c t="s" r="J220" s="7">
         <v>288</v>
-      </c>
-      <c t="s" r="J220" s="7">
-        <v>289</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8279,19 +8279,19 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
+        <v>289</v>
+      </c>
+      <c r="F222" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G222" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H222" s="8">
+        <v>270</v>
+      </c>
+      <c t="s" r="I222" s="7">
         <v>290</v>
-      </c>
-      <c r="F222" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G222" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H222" s="8">
-        <v>271</v>
-      </c>
-      <c t="s" r="I222" s="7">
-        <v>291</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>233</v>
@@ -8312,19 +8312,19 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>222</v>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8354,7 +8354,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="I224" s="7">
         <v>206</v>
@@ -8378,13 +8378,13 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>25</v>
@@ -8393,7 +8393,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8426,7 +8426,7 @@
         <v>225</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8540,7 +8540,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8567,7 +8567,7 @@
         <v>96</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c t="s" r="I231" s="7">
         <v>217</v>
@@ -8591,13 +8591,13 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>96</v>
@@ -8624,7 +8624,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8636,10 +8636,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I233" s="7">
+        <v>297</v>
+      </c>
+      <c t="s" r="J233" s="7">
         <v>298</v>
-      </c>
-      <c t="s" r="J233" s="7">
-        <v>299</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8720,7 +8720,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8885,7 +8885,7 @@
         <v>212</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8903,7 +8903,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8915,10 +8915,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I242" s="7">
+        <v>301</v>
+      </c>
+      <c t="s" r="J242" s="7">
         <v>302</v>
-      </c>
-      <c t="s" r="J242" s="7">
-        <v>303</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8963,7 +8963,7 @@
         <v>90</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>123</v>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9140,7 +9140,7 @@
         <v>37</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c t="s" r="I250" s="7">
         <v>225</v>
@@ -9164,19 +9164,19 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
+        <v>304</v>
+      </c>
+      <c r="F251" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G251" s="8">
         <v>305</v>
-      </c>
-      <c r="F251" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G251" s="8">
-        <v>306</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>98</v>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9257,7 +9257,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>47</v>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9371,7 +9371,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>114</v>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9401,7 +9401,7 @@
         <v>96</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>168</v>
@@ -9425,13 +9425,13 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>96</v>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9467,7 +9467,7 @@
         <v>96</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>162</v>
@@ -9491,19 +9491,19 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>96</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>100</v>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9539,7 +9539,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9620,7 +9620,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9719,7 +9719,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -9800,7 +9800,7 @@
         <v>243</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -9860,13 +9860,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>222</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9884,13 +9884,13 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>25</v>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -9929,7 +9929,7 @@
         <v>161</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>108</v>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -9998,22 +9998,22 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
+        <v>315</v>
+      </c>
+      <c r="F279" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G279" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H279" s="8">
         <v>316</v>
       </c>
-      <c r="F279" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G279" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H279" s="8">
+      <c t="s" r="I279" s="7">
         <v>317</v>
       </c>
-      <c t="s" r="I279" s="7">
-        <v>318</v>
-      </c>
       <c t="s" r="J279" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10031,19 +10031,19 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
+        <v>315</v>
+      </c>
+      <c r="F280" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G280" s="8">
         <v>316</v>
-      </c>
-      <c r="F280" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G280" s="8">
-        <v>317</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>167</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>131</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10073,13 +10073,13 @@
         <v>167</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10097,13 +10097,13 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
+        <v>315</v>
+      </c>
+      <c r="F282" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G282" s="8">
         <v>316</v>
-      </c>
-      <c r="F282" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G282" s="8">
-        <v>317</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>25</v>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10142,7 +10142,7 @@
         <v>90</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>22</v>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10196,19 +10196,19 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
+        <v>315</v>
+      </c>
+      <c r="F285" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G285" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H285" s="8">
         <v>316</v>
       </c>
-      <c r="F285" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G285" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H285" s="8">
-        <v>317</v>
-      </c>
       <c t="s" r="I285" s="7">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>183</v>
@@ -10229,22 +10229,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
+        <v>315</v>
+      </c>
+      <c r="F286" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G286" s="8">
         <v>316</v>
       </c>
-      <c r="F286" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G286" s="8">
-        <v>317</v>
-      </c>
       <c t="s" r="H286" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10277,19 +10277,19 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
+        <v>321</v>
+      </c>
+      <c r="F288" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G288" s="8">
         <v>322</v>
       </c>
-      <c r="F288" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G288" s="8">
+      <c t="s" r="H288" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I288" s="7">
         <v>323</v>
-      </c>
-      <c t="s" r="H288" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I288" s="7">
-        <v>324</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>210</v>
@@ -10310,22 +10310,22 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
+        <v>321</v>
+      </c>
+      <c r="F289" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G289" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H289" s="8">
         <v>322</v>
-      </c>
-      <c r="F289" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G289" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H289" s="8">
-        <v>323</v>
       </c>
       <c t="s" r="I289" s="7">
         <v>165</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10367,13 +10367,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H291" s="8">
+        <v>325</v>
+      </c>
+      <c t="s" r="I291" s="7">
         <v>326</v>
       </c>
-      <c t="s" r="I291" s="7">
-        <v>327</v>
-      </c>
       <c t="s" r="J291" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10391,13 +10391,13 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>25</v>
@@ -10424,7 +10424,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10433,13 +10433,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c t="s" r="I293" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10457,13 +10457,13 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>25</v>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10499,7 +10499,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>48</v>
@@ -10523,13 +10523,13 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>25</v>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10589,7 +10589,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10646,7 +10646,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>195</v>
@@ -10670,13 +10670,13 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>25</v>
@@ -10685,7 +10685,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -10712,7 +10712,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c t="s" r="I302" s="7">
         <v>123</v>
@@ -10736,13 +10736,13 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>25</v>
@@ -10769,7 +10769,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10778,7 +10778,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c t="s" r="I304" s="7">
         <v>47</v>
@@ -10802,13 +10802,13 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>25</v>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10844,7 +10844,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>24</v>
@@ -10868,13 +10868,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>25</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10961,7 +10961,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>180</v>
@@ -11177,7 +11177,7 @@
         <v>227</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11210,7 +11210,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -11554,13 +11554,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c t="s" r="I330" s="7">
         <v>216</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11584,7 +11584,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>37</v>
@@ -11751,7 +11751,7 @@
         <v>13</v>
       </c>
       <c r="B337" s="7">
-        <v>7712</v>
+        <v>439</v>
       </c>
       <c t="s" r="C337" s="7">
         <v>14</v>
@@ -11767,13 +11767,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>213</v>
+        <v>22</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>285</v>
+        <v>108</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11781,10 +11781,10 @@
     </row>
     <row r="338" ht="14.25" customHeight="1">
       <c t="s" r="A338" s="6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B338" s="7">
-        <v>7713</v>
+        <v>438</v>
       </c>
       <c t="s" r="C338" s="7">
         <v>14</v>
@@ -11797,98 +11797,98 @@
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>232</v>
+        <v>71</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>346</v>
+        <v>26</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c r="M338" s="7"/>
     </row>
     <row r="339" ht="14.25" customHeight="1">
-      <c r="A339" s="6"/>
-      <c r="B339" s="7"/>
-      <c r="C339" s="7"/>
+      <c t="s" r="A339" s="6">
+        <v>13</v>
+      </c>
+      <c r="B339" s="7">
+        <v>7238</v>
+      </c>
+      <c t="s" r="C339" s="7">
+        <v>14</v>
+      </c>
       <c r="D339" s="7"/>
-      <c r="E339" s="7"/>
-      <c r="F339" s="7"/>
-      <c r="G339" s="8"/>
-      <c r="H339" s="8"/>
-      <c r="I339" s="7"/>
-      <c r="J339" s="7"/>
+      <c t="s" r="E339" s="7">
+        <v>344</v>
+      </c>
+      <c r="F339" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G339" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="H339" s="8">
+        <v>252</v>
+      </c>
+      <c t="s" r="I339" s="7">
+        <v>126</v>
+      </c>
+      <c t="s" r="J339" s="7">
+        <v>241</v>
+      </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c r="M339" s="7"/>
     </row>
     <row r="340" ht="15" customHeight="1">
       <c t="s" r="A340" s="6">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B340" s="7">
-        <v>226</v>
+        <v>7239</v>
       </c>
       <c t="s" r="C340" s="7">
         <v>14</v>
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>25</v>
+        <v>252</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>317</v>
+        <v>37</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>46</v>
+        <v>346</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c r="M340" s="7"/>
     </row>
     <row r="341" ht="14.25" customHeight="1">
-      <c t="s" r="A341" s="6">
-        <v>13</v>
-      </c>
-      <c r="B341" s="7">
-        <v>225</v>
-      </c>
-      <c t="s" r="C341" s="7">
-        <v>14</v>
-      </c>
+      <c r="A341" s="6"/>
+      <c r="B341" s="7"/>
+      <c r="C341" s="7"/>
       <c r="D341" s="7"/>
-      <c t="s" r="E341" s="7">
-        <v>347</v>
-      </c>
-      <c r="F341" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G341" s="8">
-        <v>317</v>
-      </c>
-      <c t="s" r="H341" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I341" s="7">
-        <v>349</v>
-      </c>
-      <c t="s" r="J341" s="7">
-        <v>89</v>
-      </c>
+      <c r="E341" s="7"/>
+      <c r="F341" s="7"/>
+      <c r="G341" s="8"/>
+      <c r="H341" s="8"/>
+      <c r="I341" s="7"/>
+      <c r="J341" s="7"/>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c r="M341" s="7"/>
@@ -11898,7 +11898,7 @@
         <v>13</v>
       </c>
       <c r="B342" s="7">
-        <v>803</v>
+        <v>226</v>
       </c>
       <c t="s" r="C342" s="7">
         <v>14</v>
@@ -11914,13 +11914,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>211</v>
+        <v>316</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>145</v>
+        <v>348</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11931,7 +11931,7 @@
         <v>13</v>
       </c>
       <c r="B343" s="7">
-        <v>804</v>
+        <v>225</v>
       </c>
       <c t="s" r="C343" s="7">
         <v>14</v>
@@ -11944,16 +11944,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>211</v>
+        <v>316</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>224</v>
+        <v>89</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11964,7 +11964,7 @@
         <v>13</v>
       </c>
       <c r="B344" s="7">
-        <v>3948</v>
+        <v>803</v>
       </c>
       <c t="s" r="C344" s="7">
         <v>14</v>
@@ -11980,13 +11980,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>345</v>
+        <v>211</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11994,10 +11994,10 @@
     </row>
     <row r="345" ht="15" customHeight="1">
       <c t="s" r="A345" s="6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B345" s="7">
-        <v>3949</v>
+        <v>804</v>
       </c>
       <c t="s" r="C345" s="7">
         <v>14</v>
@@ -12010,98 +12010,98 @@
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>345</v>
+        <v>211</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>318</v>
+        <v>224</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c r="M345" s="7"/>
     </row>
     <row r="346" ht="14.25" customHeight="1">
-      <c r="A346" s="6"/>
-      <c r="B346" s="7"/>
-      <c r="C346" s="7"/>
+      <c t="s" r="A346" s="6">
+        <v>13</v>
+      </c>
+      <c r="B346" s="7">
+        <v>3948</v>
+      </c>
+      <c t="s" r="C346" s="7">
+        <v>14</v>
+      </c>
       <c r="D346" s="7"/>
-      <c r="E346" s="7"/>
-      <c r="F346" s="7"/>
-      <c r="G346" s="8"/>
-      <c r="H346" s="8"/>
-      <c r="I346" s="7"/>
-      <c r="J346" s="7"/>
+      <c t="s" r="E346" s="7">
+        <v>347</v>
+      </c>
+      <c r="F346" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G346" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H346" s="8">
+        <v>351</v>
+      </c>
+      <c t="s" r="I346" s="7">
+        <v>139</v>
+      </c>
+      <c t="s" r="J346" s="7">
+        <v>42</v>
+      </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c r="M346" s="7"/>
     </row>
     <row r="347" ht="14.25" customHeight="1">
       <c t="s" r="A347" s="6">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B347" s="7">
-        <v>879</v>
+        <v>3949</v>
       </c>
       <c t="s" r="C347" s="7">
         <v>14</v>
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
+        <v>347</v>
+      </c>
+      <c r="F347" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G347" s="8">
+        <v>351</v>
+      </c>
+      <c t="s" r="H347" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I347" s="7">
         <v>352</v>
       </c>
-      <c r="F347" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G347" s="8">
-        <v>64</v>
-      </c>
-      <c t="s" r="H347" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="I347" s="7">
-        <v>144</v>
-      </c>
       <c t="s" r="J347" s="7">
-        <v>129</v>
+        <v>317</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c r="M347" s="7"/>
     </row>
     <row r="348" ht="14.25" customHeight="1">
-      <c t="s" r="A348" s="6">
-        <v>13</v>
-      </c>
-      <c r="B348" s="7">
-        <v>8520</v>
-      </c>
-      <c t="s" r="C348" s="7">
-        <v>34</v>
-      </c>
+      <c r="A348" s="6"/>
+      <c r="B348" s="7"/>
+      <c r="C348" s="7"/>
       <c r="D348" s="7"/>
-      <c t="s" r="E348" s="7">
-        <v>352</v>
-      </c>
-      <c r="F348" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G348" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="H348" s="8">
-        <v>143</v>
-      </c>
-      <c t="s" r="I348" s="7">
-        <v>287</v>
-      </c>
-      <c t="s" r="J348" s="7">
-        <v>294</v>
-      </c>
+      <c r="E348" s="7"/>
+      <c r="F348" s="7"/>
+      <c r="G348" s="8"/>
+      <c r="H348" s="8"/>
+      <c r="I348" s="7"/>
+      <c r="J348" s="7"/>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c r="M348" s="7"/>
@@ -12111,29 +12111,29 @@
         <v>13</v>
       </c>
       <c r="B349" s="7">
-        <v>8521</v>
+        <v>879</v>
       </c>
       <c t="s" r="C349" s="7">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>96</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12144,14 +12144,14 @@
         <v>13</v>
       </c>
       <c r="B350" s="7">
-        <v>8020</v>
+        <v>8520</v>
       </c>
       <c t="s" r="C350" s="7">
         <v>34</v>
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12160,13 +12160,13 @@
         <v>96</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>266</v>
+        <v>143</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>171</v>
+        <v>286</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>353</v>
+        <v>293</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12174,114 +12174,114 @@
     </row>
     <row r="351" ht="14.25" customHeight="1">
       <c t="s" r="A351" s="6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B351" s="7">
-        <v>8021</v>
+        <v>8521</v>
       </c>
       <c t="s" r="C351" s="7">
         <v>34</v>
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>266</v>
+        <v>143</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>96</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>354</v>
+        <v>107</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>355</v>
+        <v>148</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c r="M351" s="7"/>
     </row>
     <row r="352" ht="14.25" customHeight="1">
-      <c r="A352" s="6"/>
-      <c r="B352" s="7"/>
-      <c r="C352" s="7"/>
+      <c t="s" r="A352" s="6">
+        <v>13</v>
+      </c>
+      <c r="B352" s="7">
+        <v>8020</v>
+      </c>
+      <c t="s" r="C352" s="7">
+        <v>34</v>
+      </c>
       <c r="D352" s="7"/>
-      <c r="E352" s="7"/>
-      <c r="F352" s="7"/>
-      <c r="G352" s="8"/>
-      <c r="H352" s="8"/>
-      <c r="I352" s="7"/>
-      <c r="J352" s="7"/>
+      <c t="s" r="E352" s="7">
+        <v>353</v>
+      </c>
+      <c r="F352" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G352" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="H352" s="8">
+        <v>265</v>
+      </c>
+      <c t="s" r="I352" s="7">
+        <v>171</v>
+      </c>
+      <c t="s" r="J352" s="7">
+        <v>354</v>
+      </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c r="M352" s="7"/>
     </row>
     <row r="353" ht="14.25" customHeight="1">
       <c t="s" r="A353" s="6">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B353" s="7">
-        <v>447</v>
+        <v>8021</v>
       </c>
       <c t="s" r="C353" s="7">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
+        <v>353</v>
+      </c>
+      <c r="F353" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G353" s="8">
+        <v>265</v>
+      </c>
+      <c t="s" r="H353" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="I353" s="7">
+        <v>355</v>
+      </c>
+      <c t="s" r="J353" s="7">
         <v>356</v>
-      </c>
-      <c r="F353" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G353" s="8">
-        <v>37</v>
-      </c>
-      <c t="s" r="H353" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I353" s="7">
-        <v>131</v>
-      </c>
-      <c t="s" r="J353" s="7">
-        <v>199</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c r="M353" s="7"/>
     </row>
     <row r="354" ht="14.25" customHeight="1">
-      <c t="s" r="A354" s="6">
-        <v>13</v>
-      </c>
-      <c r="B354" s="7">
-        <v>440</v>
-      </c>
-      <c t="s" r="C354" s="7">
-        <v>14</v>
-      </c>
+      <c r="A354" s="6"/>
+      <c r="B354" s="7"/>
+      <c r="C354" s="7"/>
       <c r="D354" s="7"/>
-      <c t="s" r="E354" s="7">
-        <v>356</v>
-      </c>
-      <c r="F354" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G354" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H354" s="8">
-        <v>37</v>
-      </c>
-      <c t="s" r="I354" s="7">
-        <v>357</v>
-      </c>
-      <c t="s" r="J354" s="7">
-        <v>77</v>
-      </c>
+      <c r="E354" s="7"/>
+      <c r="F354" s="7"/>
+      <c r="G354" s="8"/>
+      <c r="H354" s="8"/>
+      <c r="I354" s="7"/>
+      <c r="J354" s="7"/>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c r="M354" s="7"/>
@@ -12291,14 +12291,14 @@
         <v>13</v>
       </c>
       <c r="B355" s="7">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12307,13 +12307,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>135</v>
+        <v>199</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12324,45 +12324,63 @@
         <v>13</v>
       </c>
       <c r="B356" s="7">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c t="s" r="C356" s="7">
         <v>14</v>
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>225</v>
+        <v>358</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c r="M356" s="7"/>
     </row>
     <row r="357" ht="14.25" customHeight="1">
-      <c r="A357" s="6"/>
-      <c r="B357" s="7"/>
-      <c r="C357" s="7"/>
+      <c t="s" r="A357" s="6">
+        <v>13</v>
+      </c>
+      <c r="B357" s="7">
+        <v>407</v>
+      </c>
+      <c t="s" r="C357" s="7">
+        <v>14</v>
+      </c>
       <c r="D357" s="7"/>
-      <c r="E357" s="7"/>
-      <c r="F357" s="7"/>
-      <c r="G357" s="8"/>
-      <c r="H357" s="8"/>
-      <c r="I357" s="7"/>
-      <c r="J357" s="7"/>
+      <c t="s" r="E357" s="7">
+        <v>357</v>
+      </c>
+      <c r="F357" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G357" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="H357" s="8">
+        <v>169</v>
+      </c>
+      <c t="s" r="I357" s="7">
+        <v>48</v>
+      </c>
+      <c t="s" r="J357" s="7">
+        <v>135</v>
+      </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c r="M357" s="7"/>
@@ -12372,152 +12390,152 @@
         <v>13</v>
       </c>
       <c r="B358" s="7">
-        <v>5927</v>
+        <v>408</v>
       </c>
       <c t="s" r="C358" s="7">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>38</v>
+        <v>225</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>181</v>
-      </c>
-      <c t="s" r="K358" s="7">
-        <v>158</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="K358" s="7"/>
       <c r="L358" s="7"/>
-      <c t="s" r="M358" s="7">
-        <v>320</v>
-      </c>
+      <c r="M358" s="7"/>
     </row>
     <row r="359" ht="14.25" customHeight="1">
-      <c t="s" r="A359" s="6">
-        <v>13</v>
-      </c>
-      <c r="B359" s="7">
-        <v>1601</v>
-      </c>
-      <c t="s" r="C359" s="7">
-        <v>14</v>
-      </c>
+      <c r="A359" s="6"/>
+      <c r="B359" s="7"/>
+      <c r="C359" s="7"/>
       <c r="D359" s="7"/>
-      <c t="s" r="E359" s="7">
-        <v>358</v>
-      </c>
-      <c r="F359" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G359" s="8">
-        <v>115</v>
-      </c>
-      <c t="s" r="H359" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I359" s="7">
-        <v>48</v>
-      </c>
-      <c t="s" r="J359" s="7">
-        <v>159</v>
-      </c>
-      <c t="s" r="K359" s="7">
-        <v>147</v>
-      </c>
+      <c r="E359" s="7"/>
+      <c r="F359" s="7"/>
+      <c r="G359" s="8"/>
+      <c r="H359" s="8"/>
+      <c r="I359" s="7"/>
+      <c r="J359" s="7"/>
+      <c r="K359" s="7"/>
       <c r="L359" s="7"/>
-      <c t="s" r="M359" s="7">
-        <v>22</v>
-      </c>
+      <c r="M359" s="7"/>
     </row>
     <row r="360" ht="15" customHeight="1">
       <c t="s" r="A360" s="6">
         <v>13</v>
       </c>
       <c r="B360" s="7">
-        <v>1875</v>
+        <v>5927</v>
       </c>
       <c t="s" r="C360" s="7">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>359</v>
+        <v>115</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>162</v>
+        <v>38</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>246</v>
-      </c>
-      <c r="K360" s="7"/>
+        <v>181</v>
+      </c>
+      <c t="s" r="K360" s="7">
+        <v>158</v>
+      </c>
       <c r="L360" s="7"/>
-      <c r="M360" s="7"/>
+      <c t="s" r="M360" s="7">
+        <v>319</v>
+      </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
       <c t="s" r="A361" s="6">
         <v>13</v>
       </c>
       <c r="B361" s="7">
-        <v>1876</v>
+        <v>1601</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
+        <v>115</v>
+      </c>
+      <c t="s" r="H361" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I361" s="7">
+        <v>48</v>
+      </c>
+      <c t="s" r="J361" s="7">
+        <v>159</v>
+      </c>
+      <c t="s" r="K361" s="7">
+        <v>147</v>
+      </c>
+      <c r="L361" s="7"/>
+      <c t="s" r="M361" s="7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="362" ht="14.25" customHeight="1">
+      <c t="s" r="A362" s="6">
+        <v>13</v>
+      </c>
+      <c r="B362" s="7">
+        <v>1875</v>
+      </c>
+      <c t="s" r="C362" s="7">
+        <v>14</v>
+      </c>
+      <c r="D362" s="7"/>
+      <c t="s" r="E362" s="7">
         <v>359</v>
       </c>
-      <c t="s" r="H361" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I361" s="7">
-        <v>164</v>
-      </c>
-      <c t="s" r="J361" s="7">
+      <c r="F362" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G362" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H362" s="8">
         <v>360</v>
       </c>
-      <c r="K361" s="7"/>
-      <c r="L361" s="7"/>
-      <c r="M361" s="7"/>
-    </row>
-    <row r="362" ht="14.25" customHeight="1">
-      <c r="A362" s="6"/>
-      <c r="B362" s="7"/>
-      <c r="C362" s="7"/>
-      <c r="D362" s="7"/>
-      <c r="E362" s="7"/>
-      <c r="F362" s="7"/>
-      <c r="G362" s="8"/>
-      <c r="H362" s="8"/>
-      <c r="I362" s="7"/>
-      <c r="J362" s="7"/>
+      <c t="s" r="I362" s="7">
+        <v>162</v>
+      </c>
+      <c t="s" r="J362" s="7">
+        <v>260</v>
+      </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c r="M362" s="7"/>
@@ -12527,63 +12545,45 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>959</v>
+        <v>1876</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
+        <v>359</v>
+      </c>
+      <c r="F363" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G363" s="8">
+        <v>360</v>
+      </c>
+      <c t="s" r="H363" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I363" s="7">
+        <v>164</v>
+      </c>
+      <c t="s" r="J363" s="7">
         <v>361</v>
-      </c>
-      <c r="F363" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G363" s="8">
-        <v>362</v>
-      </c>
-      <c t="s" r="H363" s="8">
-        <v>37</v>
-      </c>
-      <c t="s" r="I363" s="7">
-        <v>272</v>
-      </c>
-      <c t="s" r="J363" s="7">
-        <v>124</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c r="M363" s="7"/>
     </row>
     <row r="364" ht="14.25" customHeight="1">
-      <c t="s" r="A364" s="6">
-        <v>13</v>
-      </c>
-      <c r="B364" s="7">
-        <v>143</v>
-      </c>
-      <c t="s" r="C364" s="7">
-        <v>14</v>
-      </c>
+      <c r="A364" s="6"/>
+      <c r="B364" s="7"/>
+      <c r="C364" s="7"/>
       <c r="D364" s="7"/>
-      <c t="s" r="E364" s="7">
-        <v>361</v>
-      </c>
-      <c r="F364" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G364" s="8">
-        <v>37</v>
-      </c>
-      <c t="s" r="H364" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I364" s="7">
-        <v>336</v>
-      </c>
-      <c t="s" r="J364" s="7">
-        <v>107</v>
-      </c>
+      <c r="E364" s="7"/>
+      <c r="F364" s="7"/>
+      <c r="G364" s="8"/>
+      <c r="H364" s="8"/>
+      <c r="I364" s="7"/>
+      <c r="J364" s="7"/>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c r="M364" s="7"/>
@@ -12593,29 +12593,29 @@
         <v>13</v>
       </c>
       <c r="B365" s="7">
-        <v>146</v>
+        <v>959</v>
       </c>
       <c t="s" r="C365" s="7">
         <v>14</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>25</v>
+        <v>363</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12626,14 +12626,14 @@
         <v>13</v>
       </c>
       <c r="B366" s="7">
-        <v>1127</v>
+        <v>143</v>
       </c>
       <c t="s" r="C366" s="7">
         <v>14</v>
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12645,10 +12645,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>26</v>
+        <v>336</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>207</v>
+        <v>107</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12659,14 +12659,14 @@
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>1128</v>
+        <v>146</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12678,26 +12678,44 @@
         <v>37</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>203</v>
+        <v>272</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c r="M367" s="7"/>
     </row>
     <row r="368" ht="14.25" customHeight="1">
-      <c r="A368" s="6"/>
-      <c r="B368" s="7"/>
-      <c r="C368" s="7"/>
+      <c t="s" r="A368" s="6">
+        <v>13</v>
+      </c>
+      <c r="B368" s="7">
+        <v>1127</v>
+      </c>
+      <c t="s" r="C368" s="7">
+        <v>14</v>
+      </c>
       <c r="D368" s="7"/>
-      <c r="E368" s="7"/>
-      <c r="F368" s="7"/>
-      <c r="G368" s="8"/>
-      <c r="H368" s="8"/>
-      <c r="I368" s="7"/>
-      <c r="J368" s="7"/>
+      <c t="s" r="E368" s="7">
+        <v>362</v>
+      </c>
+      <c r="F368" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G368" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="H368" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I368" s="7">
+        <v>26</v>
+      </c>
+      <c t="s" r="J368" s="7">
+        <v>207</v>
+      </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c r="M368" s="7"/>
@@ -12707,63 +12725,45 @@
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>929</v>
+        <v>1128</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H369" s="8">
         <v>37</v>
       </c>
-      <c t="s" r="H369" s="8">
-        <v>281</v>
-      </c>
       <c t="s" r="I369" s="7">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c r="M369" s="7"/>
     </row>
     <row r="370" ht="15" customHeight="1">
-      <c t="s" r="A370" s="6">
-        <v>13</v>
-      </c>
-      <c r="B370" s="7">
-        <v>928</v>
-      </c>
-      <c t="s" r="C370" s="7">
-        <v>14</v>
-      </c>
+      <c r="A370" s="6"/>
+      <c r="B370" s="7"/>
+      <c r="C370" s="7"/>
       <c r="D370" s="7"/>
-      <c t="s" r="E370" s="7">
-        <v>363</v>
-      </c>
-      <c r="F370" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G370" s="8">
-        <v>281</v>
-      </c>
-      <c t="s" r="H370" s="8">
-        <v>37</v>
-      </c>
-      <c t="s" r="I370" s="7">
-        <v>48</v>
-      </c>
-      <c t="s" r="J370" s="7">
-        <v>162</v>
-      </c>
+      <c r="E370" s="7"/>
+      <c r="F370" s="7"/>
+      <c r="G370" s="8"/>
+      <c r="H370" s="8"/>
+      <c r="I370" s="7"/>
+      <c r="J370" s="7"/>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c r="M370" s="7"/>
@@ -12773,14 +12773,14 @@
         <v>13</v>
       </c>
       <c r="B371" s="7">
-        <v>523</v>
+        <v>929</v>
       </c>
       <c t="s" r="C371" s="7">
         <v>14</v>
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12789,29 +12789,47 @@
         <v>37</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>96</v>
+        <v>280</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>213</v>
+        <v>88</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c r="M371" s="7"/>
     </row>
     <row r="372" ht="14.25" customHeight="1">
-      <c r="A372" s="6"/>
-      <c r="B372" s="7"/>
-      <c r="C372" s="7"/>
+      <c t="s" r="A372" s="6">
+        <v>13</v>
+      </c>
+      <c r="B372" s="7">
+        <v>928</v>
+      </c>
+      <c t="s" r="C372" s="7">
+        <v>14</v>
+      </c>
       <c r="D372" s="7"/>
-      <c r="E372" s="7"/>
-      <c r="F372" s="7"/>
-      <c r="G372" s="8"/>
-      <c r="H372" s="8"/>
-      <c r="I372" s="7"/>
-      <c r="J372" s="7"/>
+      <c t="s" r="E372" s="7">
+        <v>364</v>
+      </c>
+      <c r="F372" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G372" s="8">
+        <v>280</v>
+      </c>
+      <c t="s" r="H372" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="I372" s="7">
+        <v>48</v>
+      </c>
+      <c t="s" r="J372" s="7">
+        <v>162</v>
+      </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c r="M372" s="7"/>
@@ -12821,7 +12839,7 @@
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>401</v>
+        <v>523</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
@@ -12831,53 +12849,35 @@
         <v>364</v>
       </c>
       <c r="F373" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
         <v>37</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c r="M373" s="7"/>
     </row>
     <row r="374" ht="14.25" customHeight="1">
-      <c t="s" r="A374" s="6">
-        <v>13</v>
-      </c>
-      <c r="B374" s="7">
-        <v>798</v>
-      </c>
-      <c t="s" r="C374" s="7">
-        <v>14</v>
-      </c>
+      <c r="A374" s="6"/>
+      <c r="B374" s="7"/>
+      <c r="C374" s="7"/>
       <c r="D374" s="7"/>
-      <c t="s" r="E374" s="7">
-        <v>364</v>
-      </c>
-      <c r="F374" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G374" s="8">
-        <v>169</v>
-      </c>
-      <c t="s" r="H374" s="8">
-        <v>317</v>
-      </c>
-      <c t="s" r="I374" s="7">
-        <v>74</v>
-      </c>
-      <c t="s" r="J374" s="7">
-        <v>365</v>
-      </c>
+      <c r="E374" s="7"/>
+      <c r="F374" s="7"/>
+      <c r="G374" s="8"/>
+      <c r="H374" s="8"/>
+      <c r="I374" s="7"/>
+      <c r="J374" s="7"/>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c r="M374" s="7"/>
@@ -12887,29 +12887,29 @@
         <v>13</v>
       </c>
       <c r="B375" s="7">
-        <v>799</v>
+        <v>401</v>
       </c>
       <c t="s" r="C375" s="7">
         <v>14</v>
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>317</v>
+        <v>37</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>169</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12920,14 +12920,14 @@
         <v>13</v>
       </c>
       <c r="B376" s="7">
-        <v>402</v>
+        <v>798</v>
       </c>
       <c t="s" r="C376" s="7">
         <v>14</v>
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -12936,13 +12936,13 @@
         <v>169</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>37</v>
+        <v>316</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>93</v>
+        <v>366</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12953,29 +12953,29 @@
         <v>13</v>
       </c>
       <c r="B377" s="7">
-        <v>441</v>
+        <v>799</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>14</v>
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>37</v>
+        <v>316</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>273</v>
+        <v>132</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>236</v>
+        <v>133</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12986,29 +12986,29 @@
         <v>13</v>
       </c>
       <c r="B378" s="7">
-        <v>442</v>
+        <v>402</v>
       </c>
       <c t="s" r="C378" s="7">
         <v>14</v>
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13016,17 +13016,17 @@
     </row>
     <row r="379" ht="14.25" customHeight="1">
       <c t="s" r="A379" s="6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B379" s="7">
-        <v>1980</v>
+        <v>441</v>
       </c>
       <c t="s" r="C379" s="7">
         <v>14</v>
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13035,46 +13035,64 @@
         <v>37</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>366</v>
+        <v>17</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>353</v>
+        <v>272</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c r="M379" s="7"/>
     </row>
     <row r="380" ht="15" customHeight="1">
-      <c r="A380" s="6"/>
-      <c r="B380" s="7"/>
-      <c r="C380" s="7"/>
+      <c t="s" r="A380" s="6">
+        <v>13</v>
+      </c>
+      <c r="B380" s="7">
+        <v>442</v>
+      </c>
+      <c t="s" r="C380" s="7">
+        <v>14</v>
+      </c>
       <c r="D380" s="7"/>
-      <c r="E380" s="7"/>
-      <c r="F380" s="7"/>
-      <c r="G380" s="8"/>
-      <c r="H380" s="8"/>
-      <c r="I380" s="7"/>
-      <c r="J380" s="7"/>
+      <c t="s" r="E380" s="7">
+        <v>365</v>
+      </c>
+      <c r="F380" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G380" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H380" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="I380" s="7">
+        <v>201</v>
+      </c>
+      <c t="s" r="J380" s="7">
+        <v>141</v>
+      </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c r="M380" s="7"/>
     </row>
     <row r="381" ht="14.25" customHeight="1">
       <c t="s" r="A381" s="6">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B381" s="7">
-        <v>431</v>
+        <v>1980</v>
       </c>
       <c t="s" r="C381" s="7">
         <v>14</v>
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13083,47 +13101,29 @@
         <v>37</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>261</v>
+        <v>367</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>368</v>
+        <v>222</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c r="M381" s="7"/>
     </row>
     <row r="382" ht="14.25" customHeight="1">
-      <c t="s" r="A382" s="6">
-        <v>13</v>
-      </c>
-      <c r="B382" s="7">
-        <v>430</v>
-      </c>
-      <c t="s" r="C382" s="7">
-        <v>14</v>
-      </c>
+      <c r="A382" s="6"/>
+      <c r="B382" s="7"/>
+      <c r="C382" s="7"/>
       <c r="D382" s="7"/>
-      <c t="s" r="E382" s="7">
-        <v>367</v>
-      </c>
-      <c r="F382" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G382" s="8">
-        <v>261</v>
-      </c>
-      <c t="s" r="H382" s="8">
-        <v>37</v>
-      </c>
-      <c t="s" r="I382" s="7">
-        <v>87</v>
-      </c>
-      <c t="s" r="J382" s="7">
-        <v>154</v>
-      </c>
+      <c r="E382" s="7"/>
+      <c r="F382" s="7"/>
+      <c r="G382" s="8"/>
+      <c r="H382" s="8"/>
+      <c r="I382" s="7"/>
+      <c r="J382" s="7"/>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c r="M382" s="7"/>
@@ -13133,14 +13133,14 @@
         <v>13</v>
       </c>
       <c r="B383" s="7">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c t="s" r="C383" s="7">
         <v>14</v>
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13149,13 +13149,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>245</v>
+        <v>328</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>198</v>
+        <v>348</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>106</v>
+        <v>369</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13166,29 +13166,29 @@
         <v>13</v>
       </c>
       <c r="B384" s="7">
-        <v>464</v>
+        <v>430</v>
       </c>
       <c t="s" r="C384" s="7">
         <v>14</v>
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>245</v>
+        <v>328</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>369</v>
+        <v>154</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13199,14 +13199,14 @@
         <v>13</v>
       </c>
       <c r="B385" s="7">
-        <v>567</v>
+        <v>463</v>
       </c>
       <c t="s" r="C385" s="7">
         <v>14</v>
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13215,13 +13215,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>138</v>
+        <v>259</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>200</v>
+        <v>106</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13232,29 +13232,29 @@
         <v>13</v>
       </c>
       <c r="B386" s="7">
-        <v>568</v>
+        <v>464</v>
       </c>
       <c t="s" r="C386" s="7">
         <v>14</v>
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>138</v>
+        <v>259</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>40</v>
+        <v>370</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13265,14 +13265,14 @@
         <v>13</v>
       </c>
       <c r="B387" s="7">
-        <v>7238</v>
+        <v>7712</v>
       </c>
       <c t="s" r="C387" s="7">
         <v>14</v>
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13281,13 +13281,13 @@
         <v>37</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>254</v>
+        <v>351</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>126</v>
+        <v>213</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>241</v>
+        <v>284</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13298,26 +13298,26 @@
         <v>31</v>
       </c>
       <c r="B388" s="7">
-        <v>7239</v>
+        <v>7713</v>
       </c>
       <c t="s" r="C388" s="7">
         <v>14</v>
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>254</v>
+        <v>351</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>37</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>370</v>
+        <v>232</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>371</v>
@@ -13398,7 +13398,7 @@
         <v>161</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>146</v>
@@ -13461,7 +13461,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>23</v>
@@ -13491,13 +13491,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>97</v>
@@ -13533,7 +13533,7 @@
         <v>373</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13581,7 +13581,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13614,7 +13614,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13674,7 +13674,7 @@
         <v>161</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>224</v>
@@ -13704,7 +13704,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>161</v>
@@ -13713,7 +13713,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13743,7 +13743,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>164</v>
@@ -13794,7 +13794,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13956,10 +13956,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14007,7 +14007,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14169,7 +14169,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>180</v>
@@ -14280,7 +14280,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c t="s" r="I420" s="7">
         <v>46</v>
@@ -14314,7 +14314,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>25</v>
@@ -14354,7 +14354,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c t="s" r="I422" s="7">
         <v>160</v>
@@ -14384,7 +14384,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>25</v>
@@ -14456,10 +14456,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14537,7 +14537,7 @@
         <v>161</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c t="s" r="J428" s="7">
         <v>124</v>
@@ -14603,10 +14603,10 @@
         <v>96</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14702,7 +14702,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c t="s" r="J433" s="7">
         <v>81</v>
@@ -14786,7 +14786,7 @@
         <v>216</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -14816,10 +14816,10 @@
         <v>161</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -14882,7 +14882,7 @@
         <v>161</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="J439" s="7">
         <v>227</v>
@@ -14918,7 +14918,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -15065,7 +15065,7 @@
         <v>230</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15098,7 +15098,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15227,7 +15227,7 @@
         <v>37</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="J450" s="7">
         <v>164</v>
@@ -15311,7 +15311,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15344,7 +15344,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15377,7 +15377,7 @@
         <v>340</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15422,7 +15422,7 @@
         <v>386</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c t="s" r="J457" s="7">
         <v>181</v>
@@ -15584,7 +15584,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c t="s" r="J463" s="7">
         <v>217</v>
@@ -15709,7 +15709,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
@@ -15772,7 +15772,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>150</v>
@@ -15930,7 +15930,7 @@
         <v>213</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
@@ -16026,7 +16026,7 @@
         <v>402</v>
       </c>
       <c t="s" r="J478" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
@@ -16056,7 +16056,7 @@
         <v>400</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c t="s" r="J479" s="7">
         <v>193</v>
@@ -16107,7 +16107,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J481" s="7">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
@@ -16137,10 +16137,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I482" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c t="s" r="J482" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>

--- a/Data/FlightPlan/FPL_19SEP26.xlsx
+++ b/Data/FlightPlan/FPL_19SEP26.xlsx
@@ -524,6 +524,9 @@
     <t>BMV</t>
   </si>
   <si>
+    <t>07:49</t>
+  </si>
+  <si>
     <t>12:15</t>
   </si>
   <si>
@@ -806,6 +809,9 @@
     <t>05:45</t>
   </si>
   <si>
+    <t>07:43</t>
+  </si>
+  <si>
     <t>08:05</t>
   </si>
   <si>
@@ -893,6 +899,9 @@
     <t>VN-A639</t>
   </si>
   <si>
+    <t>08:09</t>
+  </si>
+  <si>
     <t>12:00</t>
   </si>
   <si>
@@ -980,6 +989,9 @@
     <t>07:05</t>
   </si>
   <si>
+    <t>07:07</t>
+  </si>
+  <si>
     <t>VN-A651</t>
   </si>
   <si>
@@ -1019,7 +1031,7 @@
     <t>VN-A656</t>
   </si>
   <si>
-    <t>06:51</t>
+    <t>06:58</t>
   </si>
   <si>
     <t>11:35</t>
@@ -1076,6 +1088,9 @@
     <t>06:05</t>
   </si>
   <si>
+    <t>07:40</t>
+  </si>
+  <si>
     <t>08:25</t>
   </si>
   <si>
@@ -1136,7 +1151,7 @@
     <t>VN-A676</t>
   </si>
   <si>
-    <t>07:40</t>
+    <t>07:47</t>
   </si>
   <si>
     <t>15:10</t>
@@ -1169,6 +1184,9 @@
     <t>VN-A687</t>
   </si>
   <si>
+    <t>06:53</t>
+  </si>
+  <si>
     <t>07:25</t>
   </si>
   <si>
@@ -1259,7 +1277,7 @@
     <t>Total Record(s): 398</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 19, 2026 05:46</t>
+    <t xml:space="preserve">Generated on  Sep 19, 2026 06:21</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4324,7 +4342,9 @@
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
+      <c t="s" r="M90" s="7">
+        <v>171</v>
+      </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c t="s" r="A91" s="6">
@@ -4386,7 +4406,7 @@
         <v>160</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4446,7 +4466,7 @@
         <v>38</v>
       </c>
       <c t="s" r="H94" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="I94" s="7">
         <v>23</v>
@@ -4476,7 +4496,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="H95" s="8">
         <v>38</v>
@@ -4515,10 +4535,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4551,7 +4571,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4584,7 +4604,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4596,7 +4616,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>74</v>
@@ -4617,7 +4637,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4632,7 +4652,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4650,7 +4670,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4662,10 +4682,10 @@
         <v>66</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4698,7 +4718,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4707,10 +4727,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>93</v>
@@ -4731,13 +4751,13 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G104" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="H104" s="8">
         <v>112</v>
@@ -4746,7 +4766,7 @@
         <v>150</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4764,7 +4784,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4773,10 +4793,10 @@
         <v>112</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>152</v>
@@ -4797,13 +4817,13 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G106" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="H106" s="8">
         <v>26</v>
@@ -4830,7 +4850,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4842,10 +4862,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4878,7 +4898,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4890,7 +4910,7 @@
         <v>164</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>47</v>
@@ -4913,7 +4933,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4946,7 +4966,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4958,10 +4978,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4979,7 +4999,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4994,7 +5014,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5012,7 +5032,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5027,7 +5047,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5045,7 +5065,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5078,7 +5098,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5087,13 +5107,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5111,22 +5131,22 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5159,7 +5179,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5171,10 +5191,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5192,7 +5212,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5204,10 +5224,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5225,7 +5245,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5240,7 +5260,7 @@
         <v>162</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5258,7 +5278,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5291,7 +5311,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5303,10 +5323,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5324,7 +5344,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5336,10 +5356,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5372,7 +5392,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5387,7 +5407,7 @@
         <v>44</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5405,7 +5425,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5417,7 +5437,7 @@
         <v>104</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>141</v>
@@ -5438,7 +5458,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5453,7 +5473,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5471,7 +5491,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5480,7 +5500,7 @@
         <v>38</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="I128" s="7">
         <v>134</v>
@@ -5519,7 +5539,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5534,7 +5554,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5552,7 +5572,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5561,13 +5581,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="I131" s="7">
         <v>115</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5585,19 +5605,19 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>147</v>
@@ -5618,7 +5638,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5633,7 +5653,7 @@
         <v>168</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5666,7 +5686,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5675,13 +5695,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="I135" s="7">
         <v>62</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5699,22 +5719,22 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5747,7 +5767,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5759,17 +5779,17 @@
         <v>122</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="K138" s="7">
         <v>18</v>
       </c>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -5784,7 +5804,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5796,10 +5816,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5817,7 +5837,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5826,13 +5846,13 @@
         <v>38</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="I140" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5850,22 +5870,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5898,7 +5918,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5910,7 +5930,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J143" s="7">
         <v>151</v>
@@ -5931,7 +5951,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5946,14 +5966,14 @@
         <v>151</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="K144" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -5968,7 +5988,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5980,7 +6000,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>99</v>
@@ -6005,7 +6025,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6014,20 +6034,20 @@
         <v>38</v>
       </c>
       <c t="s" r="H146" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="K146" s="7">
         <v>165</v>
       </c>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6042,25 +6062,25 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G147" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="H147" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="K147" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
@@ -6094,7 +6114,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6106,10 +6126,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6127,7 +6147,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6160,7 +6180,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6175,7 +6195,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6193,7 +6213,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6205,10 +6225,10 @@
         <v>56</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6241,19 +6261,19 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>139</v>
@@ -6274,7 +6294,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6289,7 +6309,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6307,7 +6327,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6322,7 +6342,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6355,7 +6375,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6364,7 +6384,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I158" s="7">
         <v>57</v>
@@ -6373,7 +6393,7 @@
         <v>107</v>
       </c>
       <c t="s" r="K158" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
@@ -6392,29 +6412,29 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="K159" s="7">
         <v>22</v>
       </c>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -6429,7 +6449,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6438,13 +6458,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I160" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6462,22 +6482,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6510,7 +6530,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6519,13 +6539,13 @@
         <v>38</v>
       </c>
       <c t="s" r="H163" s="8">
+        <v>173</v>
+      </c>
+      <c t="s" r="I163" s="7">
+        <v>208</v>
+      </c>
+      <c t="s" r="J163" s="7">
         <v>172</v>
-      </c>
-      <c t="s" r="I163" s="7">
-        <v>207</v>
-      </c>
-      <c t="s" r="J163" s="7">
-        <v>171</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6543,13 +6563,13 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>38</v>
@@ -6558,7 +6578,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6576,7 +6596,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6588,7 +6608,7 @@
         <v>143</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>51</v>
@@ -6609,7 +6629,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6642,7 +6662,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6654,10 +6674,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6690,7 +6710,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6702,15 +6722,15 @@
         <v>38</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -6725,7 +6745,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6737,7 +6757,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>79</v>
@@ -6758,7 +6778,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6770,7 +6790,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>59</v>
@@ -6791,7 +6811,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6803,10 +6823,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6824,7 +6844,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6833,7 +6853,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>146</v>
@@ -6857,22 +6877,22 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6905,7 +6925,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6917,14 +6937,16 @@
         <v>122</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>68</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
-      <c r="M176" s="7"/>
+      <c t="s" r="M176" s="7">
+        <v>266</v>
+      </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c t="s" r="A177" s="6">
@@ -6938,7 +6960,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6950,10 +6972,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6971,7 +6993,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6980,7 +7002,7 @@
         <v>38</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>19</v>
@@ -7004,19 +7026,19 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>140</v>
@@ -7037,7 +7059,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7046,7 +7068,7 @@
         <v>38</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="I180" s="7">
         <v>82</v>
@@ -7070,13 +7092,13 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>38</v>
@@ -7085,7 +7107,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7118,7 +7140,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7130,7 +7152,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>71</v>
@@ -7151,7 +7173,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7184,7 +7206,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7217,7 +7239,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7226,10 +7248,10 @@
         <v>122</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>110</v>
@@ -7250,19 +7272,19 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>122</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>155</v>
@@ -7283,7 +7305,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7298,7 +7320,7 @@
         <v>146</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7316,7 +7338,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7325,10 +7347,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>86</v>
@@ -7349,22 +7371,22 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7397,7 +7419,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7406,10 +7428,10 @@
         <v>38</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>105</v>
@@ -7430,22 +7452,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7463,7 +7485,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7478,7 +7500,7 @@
         <v>131</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7496,7 +7518,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7511,7 +7533,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7529,7 +7551,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7544,7 +7566,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7562,7 +7584,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7574,10 +7596,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7610,7 +7632,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7622,7 +7644,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>91</v>
@@ -7643,7 +7665,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7658,7 +7680,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7676,7 +7698,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7685,10 +7707,10 @@
         <v>112</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>131</v>
@@ -7709,22 +7731,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>112</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7742,7 +7764,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7757,7 +7779,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7775,7 +7797,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7787,7 +7809,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>165</v>
@@ -7808,7 +7830,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7820,10 +7842,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7856,7 +7878,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7868,7 +7890,7 @@
         <v>170</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>47</v>
@@ -7889,7 +7911,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7904,7 +7926,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7922,7 +7944,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7931,10 +7953,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>49</v>
@@ -7955,13 +7977,13 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>26</v>
@@ -7988,7 +8010,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8000,7 +8022,7 @@
         <v>170</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>41</v>
@@ -8021,7 +8043,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8054,7 +8076,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8066,7 +8088,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>85</v>
@@ -8087,7 +8109,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8102,7 +8124,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8135,7 +8157,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8154,7 +8176,9 @@
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
-      <c r="M216" s="7"/>
+      <c t="s" r="M216" s="7">
+        <v>296</v>
+      </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c t="s" r="A217" s="6">
@@ -8168,7 +8192,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8183,7 +8207,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8201,7 +8225,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8234,7 +8258,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8246,7 +8270,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>73</v>
@@ -8267,7 +8291,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8276,10 +8300,10 @@
         <v>38</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>24</v>
@@ -8300,13 +8324,13 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>38</v>
@@ -8315,7 +8339,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8333,7 +8357,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8342,13 +8366,13 @@
         <v>38</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="I222" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8366,22 +8390,22 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8414,7 +8438,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8423,17 +8447,21 @@
         <v>26</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>238</v>
-      </c>
-      <c r="K225" s="7"/>
+        <v>239</v>
+      </c>
+      <c t="s" r="K225" s="7">
+        <v>221</v>
+      </c>
       <c r="L225" s="7"/>
-      <c r="M225" s="7"/>
+      <c t="s" r="M225" s="7">
+        <v>302</v>
+      </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c t="s" r="A226" s="6">
@@ -8447,26 +8475,30 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>223</v>
-      </c>
-      <c r="K226" s="7"/>
+        <v>224</v>
+      </c>
+      <c t="s" r="K226" s="7">
+        <v>130</v>
+      </c>
       <c r="L226" s="7"/>
-      <c r="M226" s="7"/>
+      <c t="s" r="M226" s="7">
+        <v>39</v>
+      </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
       <c t="s" r="A227" s="6">
@@ -8480,7 +8512,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8489,10 +8521,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>81</v>
@@ -8513,13 +8545,13 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>26</v>
@@ -8528,7 +8560,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8546,7 +8578,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8555,7 +8587,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="I229" s="7">
         <v>163</v>
@@ -8579,13 +8611,13 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>26</v>
@@ -8612,7 +8644,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8645,7 +8677,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8657,10 +8689,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8693,7 +8725,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8705,10 +8737,10 @@
         <v>164</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8726,7 +8758,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8741,7 +8773,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8759,7 +8791,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8768,10 +8800,10 @@
         <v>112</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>50</v>
@@ -8792,19 +8824,19 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>112</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>74</v>
@@ -8825,7 +8857,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8837,10 +8869,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I238" s="7">
+        <v>310</v>
+      </c>
+      <c t="s" r="J238" s="7">
         <v>307</v>
-      </c>
-      <c t="s" r="J238" s="7">
-        <v>304</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8873,7 +8905,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8906,7 +8938,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8921,7 +8953,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8939,7 +8971,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8972,7 +9004,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9005,7 +9037,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9017,7 +9049,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>141</v>
@@ -9038,7 +9070,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9050,7 +9082,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>165</v>
@@ -9071,7 +9103,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9083,10 +9115,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9104,7 +9136,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9116,10 +9148,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9152,7 +9184,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9164,7 +9196,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>130</v>
@@ -9185,7 +9217,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9218,7 +9250,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9251,7 +9283,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9299,7 +9331,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9332,7 +9364,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9341,7 +9373,7 @@
         <v>38</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="I255" s="7">
         <v>99</v>
@@ -9365,19 +9397,19 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>102</v>
@@ -9398,7 +9430,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9446,19 +9478,19 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>96</v>
@@ -9479,7 +9511,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9488,10 +9520,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>57</v>
@@ -9527,7 +9559,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9539,10 +9571,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9560,7 +9592,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9572,7 +9604,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>121</v>
@@ -9593,7 +9625,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9602,10 +9634,10 @@
         <v>112</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>50</v>
@@ -9626,13 +9658,13 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>112</v>
@@ -9659,7 +9691,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9668,7 +9700,7 @@
         <v>112</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>165</v>
@@ -9692,22 +9724,22 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>112</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9725,7 +9757,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9740,7 +9772,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9773,7 +9805,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9806,7 +9838,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9821,7 +9853,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9839,7 +9871,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9848,7 +9880,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>109</v>
@@ -9872,13 +9904,13 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>26</v>
@@ -9887,7 +9919,7 @@
         <v>162</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9905,7 +9937,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9920,7 +9952,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9938,7 +9970,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9950,10 +9982,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9986,7 +10018,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -9995,17 +10027,19 @@
         <v>26</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
-      <c r="M277" s="7"/>
+      <c t="s" r="M277" s="7">
+        <v>326</v>
+      </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
       <c t="s" r="A278" s="6">
@@ -10019,13 +10053,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>26</v>
@@ -10034,7 +10068,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10052,7 +10086,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10061,13 +10095,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10085,13 +10119,13 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>26</v>
@@ -10100,7 +10134,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10118,7 +10152,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10130,7 +10164,7 @@
         <v>164</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>115</v>
@@ -10151,7 +10185,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10166,7 +10200,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10199,7 +10233,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10208,18 +10242,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10234,19 +10268,19 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>170</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>105</v>
@@ -10267,7 +10301,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10276,13 +10310,13 @@
         <v>170</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10300,13 +10334,13 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>26</v>
@@ -10333,7 +10367,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10345,7 +10379,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>23</v>
@@ -10366,7 +10400,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10378,10 +10412,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10399,7 +10433,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10408,13 +10442,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10432,22 +10466,22 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10480,22 +10514,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10513,7 +10547,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10522,13 +10556,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>168</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10561,7 +10595,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10570,13 +10604,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10596,22 +10630,22 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10629,7 +10663,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10638,13 +10672,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10662,13 +10696,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>26</v>
@@ -10695,7 +10729,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10704,10 +10738,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J300" s="7">
         <v>140</v>
@@ -10728,13 +10762,13 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>26</v>
@@ -10743,7 +10777,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10761,7 +10795,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -10773,10 +10807,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10794,7 +10828,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -10809,7 +10843,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10842,7 +10876,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10851,18 +10885,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -10877,22 +10911,22 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G306" s="8">
+        <v>305</v>
+      </c>
+      <c t="s" r="H306" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I306" s="7">
+        <v>221</v>
+      </c>
+      <c t="s" r="J306" s="7">
         <v>302</v>
-      </c>
-      <c t="s" r="H306" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I306" s="7">
-        <v>220</v>
-      </c>
-      <c t="s" r="J306" s="7">
-        <v>299</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10910,7 +10944,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10919,7 +10953,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="I307" s="7">
         <v>130</v>
@@ -10943,13 +10977,13 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>26</v>
@@ -10958,7 +10992,7 @@
         <v>160</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10976,7 +11010,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -10985,13 +11019,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="I309" s="7">
         <v>96</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -11009,22 +11043,22 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11042,7 +11076,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11051,13 +11085,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11075,13 +11109,13 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>26</v>
@@ -11090,7 +11124,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11108,7 +11142,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11120,10 +11154,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11156,7 +11190,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11168,15 +11202,15 @@
         <v>38</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11191,7 +11225,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11203,7 +11237,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>81</v>
@@ -11224,7 +11258,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11236,7 +11270,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>98</v>
@@ -11257,7 +11291,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11272,7 +11306,7 @@
         <v>162</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11305,7 +11339,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11338,7 +11372,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11350,10 +11384,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11371,7 +11405,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11383,10 +11417,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11404,7 +11438,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11416,10 +11450,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11452,7 +11486,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11464,10 +11498,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11485,7 +11519,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11497,7 +11531,7 @@
         <v>80</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>58</v>
@@ -11518,7 +11552,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11566,7 +11600,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11581,7 +11615,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11599,7 +11633,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11632,7 +11666,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11680,7 +11714,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11689,13 +11723,13 @@
         <v>38</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11713,19 +11747,19 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>48</v>
@@ -11746,7 +11780,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11758,7 +11792,7 @@
         <v>122</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>123</v>
@@ -11779,7 +11813,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11812,7 +11846,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -11824,7 +11858,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>155</v>
@@ -11845,7 +11879,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11857,7 +11891,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>42</v>
@@ -11893,7 +11927,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11902,7 +11936,7 @@
         <v>38</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>23</v>
@@ -11926,13 +11960,13 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>38</v>
@@ -11959,7 +11993,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -11968,13 +12002,13 @@
         <v>38</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>133</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11992,22 +12026,22 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12040,7 +12074,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12049,17 +12083,19 @@
         <v>26</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>57</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
-      <c r="M345" s="7"/>
+      <c t="s" r="M345" s="7">
+        <v>359</v>
+      </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
       <c t="s" r="A346" s="6">
@@ -12073,19 +12109,19 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>93</v>
@@ -12106,7 +12142,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12115,7 +12151,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>150</v>
@@ -12139,22 +12175,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12172,7 +12208,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12181,7 +12217,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c t="s" r="I349" s="7">
         <v>144</v>
@@ -12205,22 +12241,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12253,7 +12289,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12273,7 +12309,7 @@
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -12288,7 +12324,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12300,10 +12336,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12321,7 +12357,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12354,7 +12390,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12363,13 +12399,13 @@
         <v>112</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12387,22 +12423,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>112</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12435,7 +12471,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12450,7 +12486,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12468,7 +12504,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12480,7 +12516,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>81</v>
@@ -12501,7 +12537,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12510,10 +12546,10 @@
         <v>38</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>140</v>
@@ -12534,13 +12570,13 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>38</v>
@@ -12549,7 +12585,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12582,7 +12618,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12597,14 +12633,14 @@
         <v>39</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="K363" s="7">
         <v>160</v>
       </c>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -12619,7 +12655,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
@@ -12631,7 +12667,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J364" s="7">
         <v>161</v>
@@ -12656,7 +12692,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12665,13 +12701,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c t="s" r="I365" s="7">
         <v>165</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12689,13 +12725,13 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>26</v>
@@ -12704,7 +12740,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12737,19 +12773,19 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>131</v>
@@ -12770,7 +12806,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12782,7 +12818,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>114</v>
@@ -12803,7 +12839,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12815,7 +12851,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J370" s="7">
         <v>41</v>
@@ -12836,7 +12872,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12851,7 +12887,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12869,7 +12905,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12917,7 +12953,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12926,7 +12962,7 @@
         <v>38</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>92</v>
@@ -12950,19 +12986,19 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>165</v>
@@ -12983,7 +13019,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -12995,7 +13031,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>133</v>
@@ -13031,7 +13067,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13040,7 +13076,7 @@
         <v>38</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="I378" s="7">
         <v>149</v>
@@ -13064,22 +13100,22 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I379" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13097,16 +13133,16 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="I380" s="7">
         <v>138</v>
@@ -13130,13 +13166,13 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>38</v>
@@ -13163,7 +13199,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13175,7 +13211,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>101</v>
@@ -13196,7 +13232,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13229,7 +13265,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13238,13 +13274,13 @@
         <v>38</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13277,7 +13313,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13286,17 +13322,19 @@
         <v>38</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
-      <c r="M386" s="7"/>
+      <c t="s" r="M386" s="7">
+        <v>380</v>
+      </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
       <c t="s" r="A387" s="6">
@@ -13310,13 +13348,13 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>38</v>
@@ -13343,7 +13381,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -13352,10 +13390,10 @@
         <v>38</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>113</v>
@@ -13376,13 +13414,13 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>38</v>
@@ -13391,7 +13429,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13409,7 +13447,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13418,13 +13456,13 @@
         <v>38</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13442,22 +13480,22 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13490,7 +13528,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13505,7 +13543,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13523,7 +13561,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13535,7 +13573,7 @@
         <v>164</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>151</v>
@@ -13556,7 +13594,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13589,7 +13627,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13598,13 +13636,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="I396" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13622,13 +13660,13 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="H397" s="8">
         <v>26</v>
@@ -13655,7 +13693,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13667,10 +13705,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13703,7 +13741,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13715,15 +13753,15 @@
         <v>164</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -13738,7 +13776,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13753,7 +13791,7 @@
         <v>95</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13771,7 +13809,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13786,7 +13824,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13804,7 +13842,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13813,10 +13851,10 @@
         <v>164</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>110</v>
@@ -13837,13 +13875,13 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>164</v>
@@ -13852,7 +13890,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13870,7 +13908,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -13882,7 +13920,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>167</v>
@@ -13918,7 +13956,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13927,13 +13965,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>71</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13951,13 +13989,13 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>26</v>
@@ -13984,7 +14022,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -13996,7 +14034,7 @@
         <v>143</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>23</v>
@@ -14017,7 +14055,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14029,10 +14067,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14050,7 +14088,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14083,7 +14121,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14095,10 +14133,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14131,7 +14169,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14146,7 +14184,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14164,7 +14202,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14179,7 +14217,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14197,7 +14235,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14230,7 +14268,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14263,7 +14301,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14278,7 +14316,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14296,7 +14334,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14308,10 +14346,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14344,7 +14382,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14356,7 +14394,7 @@
         <v>143</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>44</v>
@@ -14364,7 +14402,7 @@
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>336</v>
+        <v>391</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -14379,7 +14417,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -14391,7 +14429,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>130</v>
@@ -14412,7 +14450,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -14421,20 +14459,20 @@
         <v>26</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="K423" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -14449,13 +14487,13 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>17</v>
@@ -14464,14 +14502,14 @@
         <v>139</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="K424" s="7">
         <v>106</v>
       </c>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -14486,7 +14524,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14495,10 +14533,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>60</v>
@@ -14519,13 +14557,13 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>26</v>
@@ -14534,7 +14572,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14567,7 +14605,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -14600,7 +14638,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
@@ -14612,7 +14650,7 @@
         <v>164</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>131</v>
@@ -14633,7 +14671,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F430" s="7">
         <v>320</v>
@@ -14645,10 +14683,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14666,7 +14704,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -14678,10 +14716,10 @@
         <v>112</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14699,7 +14737,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
@@ -14711,7 +14749,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c t="s" r="J432" s="7">
         <v>60</v>
@@ -14732,7 +14770,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F433" s="7">
         <v>320</v>
@@ -14747,7 +14785,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14765,7 +14803,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F434" s="7">
         <v>320</v>
@@ -14777,7 +14815,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J434" s="7">
         <v>85</v>
@@ -14798,7 +14836,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F435" s="7">
         <v>320</v>
@@ -14846,7 +14884,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -14858,15 +14896,15 @@
         <v>122</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -14881,7 +14919,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -14893,10 +14931,10 @@
         <v>164</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -14914,7 +14952,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -14923,7 +14961,7 @@
         <v>164</v>
       </c>
       <c t="s" r="H439" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="I439" s="7">
         <v>96</v>
@@ -14947,22 +14985,22 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="H440" s="8">
         <v>164</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -14980,7 +15018,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -14995,7 +15033,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -15013,7 +15051,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -15028,7 +15066,7 @@
         <v>63</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -15061,7 +15099,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -15081,7 +15119,7 @@
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>322</v>
+        <v>347</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -15096,7 +15134,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
@@ -15129,7 +15167,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -15141,10 +15179,10 @@
         <v>143</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15162,7 +15200,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -15177,7 +15215,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15195,7 +15233,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -15207,7 +15245,7 @@
         <v>112</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>59</v>
@@ -15228,7 +15266,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -15240,7 +15278,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c t="s" r="J449" s="7">
         <v>110</v>
@@ -15261,7 +15299,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
@@ -15294,7 +15332,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F451" s="7">
         <v>321</v>
@@ -15306,7 +15344,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c t="s" r="J451" s="7">
         <v>167</v>
@@ -15342,7 +15380,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
@@ -15357,7 +15395,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15375,7 +15413,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
@@ -15390,7 +15428,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15408,7 +15446,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
@@ -15423,7 +15461,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15441,7 +15479,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F456" s="7">
         <v>320</v>
@@ -15453,10 +15491,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15489,7 +15527,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
@@ -15498,13 +15536,13 @@
         <v>112</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15522,13 +15560,13 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c t="s" r="H459" s="8">
         <v>112</v>
@@ -15537,7 +15575,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -15570,7 +15608,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
@@ -15579,13 +15617,13 @@
         <v>112</v>
       </c>
       <c t="s" r="H461" s="8">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15603,22 +15641,22 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="F462" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G462" s="8">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c t="s" r="H462" s="8">
         <v>112</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
@@ -15651,7 +15689,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
@@ -15663,17 +15701,17 @@
         <v>112</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="K464" s="7">
         <v>138</v>
       </c>
       <c r="L464" s="7"/>
       <c t="s" r="M464" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="465" ht="15" customHeight="1">
@@ -15688,7 +15726,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="F465" s="7">
         <v>330</v>
@@ -15697,7 +15735,7 @@
         <v>112</v>
       </c>
       <c t="s" r="H465" s="8">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c t="s" r="I465" s="7">
         <v>50</v>
@@ -15706,11 +15744,11 @@
         <v>42</v>
       </c>
       <c t="s" r="K465" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L465" s="7"/>
       <c t="s" r="M465" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="466" ht="14.25" customHeight="1">
@@ -15725,19 +15763,19 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G466" s="8">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c t="s" r="H466" s="8">
         <v>112</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J466" s="7">
         <v>127</v>
@@ -15773,7 +15811,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F468" s="7">
         <v>330</v>
@@ -15785,15 +15823,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
       <c t="s" r="M468" s="7">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="469" ht="14.25" customHeight="1">
@@ -15808,7 +15846,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
@@ -15823,7 +15861,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
@@ -15841,7 +15879,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
@@ -15853,17 +15891,17 @@
         <v>26</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c t="s" r="J470" s="7">
         <v>106</v>
       </c>
       <c t="s" r="K470" s="7">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -15878,7 +15916,7 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F471" s="7">
         <v>330</v>
@@ -15911,11 +15949,11 @@
         <v>34</v>
       </c>
       <c t="s" r="C472" s="7">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F472" s="7">
         <v>330</v>
@@ -15924,13 +15962,13 @@
         <v>38</v>
       </c>
       <c t="s" r="H472" s="8">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c t="s" r="I472" s="7">
         <v>167</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
@@ -15963,7 +16001,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F474" s="7">
         <v>330</v>
@@ -15978,7 +16016,7 @@
         <v>72</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
@@ -15996,7 +16034,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F475" s="7">
         <v>330</v>
@@ -16005,13 +16043,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H475" s="8">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c t="s" r="I475" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
@@ -16044,7 +16082,7 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="F477" s="7">
         <v>330</v>
@@ -16092,22 +16130,22 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="F479" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G479" s="8">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c t="s" r="H479" s="8">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
@@ -16125,7 +16163,7 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="F480" s="7">
         <v>330</v>
@@ -16134,13 +16172,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H480" s="8">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c t="s" r="I480" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
@@ -16173,7 +16211,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="F482" s="7">
         <v>330</v>
@@ -16182,13 +16220,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H482" s="8">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c t="s" r="I482" s="7">
         <v>93</v>
       </c>
       <c t="s" r="J482" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
@@ -16206,22 +16244,22 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="F483" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G483" s="8">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c t="s" r="H483" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I483" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="J483" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
@@ -16229,7 +16267,7 @@
     </row>
     <row r="484" ht="15.75" customHeight="1">
       <c t="s" r="A484" s="9">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B484" s="9"/>
       <c r="C484" s="9"/>
@@ -16249,7 +16287,7 @@
     <row r="485" ht="66" customHeight="1"/>
     <row r="486" ht="16.5" customHeight="1">
       <c t="s" r="A486" s="10">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B486" s="10"/>
       <c r="C486" s="10"/>
@@ -16262,7 +16300,7 @@
       <c r="J486" s="10"/>
       <c r="K486" s="10"/>
       <c t="s" r="L486" s="11">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="M486" s="11"/>
       <c r="N486" s="11"/>
